--- a/resources/i18n/translations_master.xlsx
+++ b/resources/i18n/translations_master.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rb0d2781adf8a4f3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="R53b4214a54724c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="R87228943cdb8488d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="R08cf151aa3624060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rf93f165648e5486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="Rfffc0bd185a64a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="R75ed1cf4f60449ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="R0081423c699c4660"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -970,16 +970,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>ex : une astronaute timide passionnée de plantes, ton doux et curieux</x:v>
+        <x:v>Décris brièvement le personnage, son rôle et son ton…</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>e.g.: a shy astronaut passionate about plants, gentle and curious tone</x:v>
+        <x:v>Briefly describe the character, their role and tone…</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>ej: una astronauta tímida apasionada por las plantas, tono dulce y curioso</x:v>
+        <x:v>Describe brevemente el personaje, su rol y su tono…</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>z.B.: eine schüchterne Astronautin mit Leidenschaft für Pflanzen, sanfter und neugieriger Ton</x:v>
+        <x:v>Beschreibe kurz den Charakter, seine Rolle und seinen Ton…</x:v>
       </x:c>
       <x:c r="H20" s="4"/>
       <x:c r="I20" s="4"/>
@@ -1026,16 +1026,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>ex : Mia</x:v>
+        <x:v>Nom du personnage</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>e.g.: Mia</x:v>
+        <x:v>Character name</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>ej: Mia</x:v>
+        <x:v>Nombre del personaje</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>z.B.: Mia</x:v>
+        <x:v>Charaktername</x:v>
       </x:c>
       <x:c r="H22" s="4"/>
       <x:c r="I22" s="4"/>
@@ -1222,16 +1222,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>ex : amant, mentor, rival, ami…</x:v>
+        <x:v>ex : ami, guide, collègue…</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>e.g.: lover, mentor, rival, friend…</x:v>
+        <x:v>e.g. friend, guide, colleague…</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
-        <x:v>ej: amante, mentor, rival, amigo…</x:v>
+        <x:v>p. ej.: amigo, guía, colega…</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>e.g.: lover, mentor, rival, friend…</x:v>
+        <x:v>z. B.: Freund, Begleiter, Kollege…</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -1308,20 +1308,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>ex : Je ne supporte pas qu'on crache en public.
-La politique m'ennuie profondément.</x:v>
+        <x:v>Décris les sujets, comportements ou limites à éviter…</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>e.g.: I can't stand people spitting in public.
-Politics bores me deeply.</x:v>
+        <x:v>Describe topics, behaviors or limits to avoid…</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>e.g.: I can't stand people spitting in public.
-Politics bores me deeply.</x:v>
+        <x:v>Describe temas, comportamientos o límites que deben evitarse…</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>e.g.: I can't stand people spitting in public.
-Politics bores me deeply.</x:v>
+        <x:v>Beschreibe Themen, Verhaltensweisen oder Grenzen, die vermieden werden sollen…</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -1510,16 +1506,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>ex : a woman, curvy figure, large breasts, long hair</x:v>
+        <x:v>ex : adult character, short hair, blue eyes</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>e.g.: a woman, curvy figure, large breasts, long hair</x:v>
+        <x:v>e.g. adult character, short hair, blue eyes</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>e.g.: a woman, curvy figure, large breasts, long hair</x:v>
+        <x:v>p. ej.: adult character, short hair, blue eyes</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>e.g.: a woman, curvy figure, large breasts, long hair</x:v>
+        <x:v>z. B.: adult character, short hair, blue eyes</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -1772,16 +1768,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
-        <x:v>Variante…</x:v>
+        <x:v>Choisir une variante…</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>Variant…</x:v>
+        <x:v>Choose a variant…</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>Variant…</x:v>
+        <x:v>Elegir una variante…</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
-        <x:v>Variant…</x:v>
+        <x:v>Variante auswählen…</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -2618,16 +2614,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
-        <x:v>une par ligne</x:v>
+        <x:v>un élément par ligne</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>one item per line</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>un elemento por línea</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>ein Eintrag pro Zeile</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -2678,16 +2674,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
-        <x:v>une par ligne</x:v>
+        <x:v>un élément par ligne</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>one item per line</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>un elemento por línea</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>ein Eintrag pro Zeile</x:v>
       </x:c>
       <x:c r="H78" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -2738,16 +2734,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>un par ligne</x:v>
+        <x:v>un événement par ligne</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>one event per line</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>un evento por línea</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>ein Ereignis pro Zeile</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -2798,16 +2794,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
-        <x:v>une par ligne</x:v>
+        <x:v>une préférence par ligne</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>one preference per line</x:v>
       </x:c>
       <x:c r="F82" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>una preferencia por línea</x:v>
       </x:c>
       <x:c r="G82" s="4" t="str">
-        <x:v>one per line</x:v>
+        <x:v>eine Präferenz pro Zeile</x:v>
       </x:c>
       <x:c r="H82" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -2858,16 +2854,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
-        <x:v>résumé de la relation actuelle</x:v>
+        <x:v>Résumé de la relation actuelle…</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>summary of the current relationship</x:v>
+        <x:v>Summary of the current relationship…</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
-        <x:v>summary of the current relationship</x:v>
+        <x:v>Resumen de la relación actual…</x:v>
       </x:c>
       <x:c r="G84" s="4" t="str">
-        <x:v>summary of the current relationship</x:v>
+        <x:v>Zusammenfassung der aktuellen Beziehung…</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -2978,16 +2974,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
-        <x:v>auto-mis à jour</x:v>
+        <x:v>Mis à jour automatiquement</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>auto-updated</x:v>
+        <x:v>Updated automatically</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
-        <x:v>auto-updated</x:v>
+        <x:v>Se actualiza automáticamente</x:v>
       </x:c>
       <x:c r="G88" s="4" t="str">
-        <x:v>auto-updated</x:v>
+        <x:v>Wird automatisch aktualisiert</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -3038,16 +3034,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>ex : chaleureuse, tendue…</x:v>
+        <x:v>ex : amicale, distante, tendue…</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>e.g.: warm, tense…</x:v>
+        <x:v>e.g. friendly, distant, tense…</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
-        <x:v>e.g.: warm, tense…</x:v>
+        <x:v>p. ej.: amistosa, distante, tensa…</x:v>
       </x:c>
       <x:c r="G90" s="4" t="str">
-        <x:v>e.g.: warm, tense…</x:v>
+        <x:v>z. B.: freundlich, distanziert, angespannt…</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -3158,16 +3154,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D94" s="4" t="str">
-        <x:v>Ajouter un souvenir / fait à retenir…</x:v>
+        <x:v>Ajouter un souvenir ou un fait à retenir…</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>Add a memory / fact to remember…</x:v>
+        <x:v>Add a memory or fact to remember…</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>Add a memory / fact to remember…</x:v>
+        <x:v>Añadir un recuerdo o dato importante…</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
-        <x:v>Add a memory / fact to remember…</x:v>
+        <x:v>Erinnerung oder wichtigen Fakt hinzufügen…</x:v>
       </x:c>
       <x:c r="H94" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -4068,16 +4064,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D125" s="4" t="str">
-        <x:v>Ton message…</x:v>
+        <x:v>Écris un message…</x:v>
       </x:c>
       <x:c r="E125" s="4" t="str">
-        <x:v>Your message…</x:v>
+        <x:v>Write a message…</x:v>
       </x:c>
       <x:c r="F125" s="4" t="str">
-        <x:v>Tu mensaje…</x:v>
+        <x:v>Escribe un mensaje…</x:v>
       </x:c>
       <x:c r="G125" s="4" t="str">
-        <x:v>Deine Nachricht…</x:v>
+        <x:v>Nachricht schreiben…</x:v>
       </x:c>
       <x:c r="H125" s="4" t="str">
         <x:v>V39 translated core chat + scenario</x:v>
@@ -4308,16 +4304,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D133" s="2" t="str">
-        <x:v>ex : Nuit de pluie</x:v>
+        <x:v>ex : Première rencontre</x:v>
       </x:c>
       <x:c r="E133" s="2" t="str">
-        <x:v>e.g.: Rainy Night</x:v>
+        <x:v>e.g. First meeting</x:v>
       </x:c>
       <x:c r="F133" s="2" t="str">
-        <x:v>p. ej.: Noche lluviosa</x:v>
+        <x:v>p. ej.: Primer encuentro</x:v>
       </x:c>
       <x:c r="G133" s="2" t="str">
-        <x:v>z. B.: Regnerische Nacht</x:v>
+        <x:v>z. B.: Erstes Treffen</x:v>
       </x:c>
       <x:c r="H133" s="2" t="str">
         <x:v>V39 translated core chat + scenario</x:v>
@@ -4608,16 +4604,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D143" s="2" t="str">
-        <x:v>ex : Faire avouer ses sentiments</x:v>
+        <x:v>ex : Accomplir une tâche commune</x:v>
       </x:c>
       <x:c r="E143" s="2" t="str">
-        <x:v>e.g.: Make them confess their feelings</x:v>
+        <x:v>e.g. Complete a shared task</x:v>
       </x:c>
       <x:c r="F143" s="2" t="str">
-        <x:v>p. ej.: Hacerle confesar sus sentimientos</x:v>
+        <x:v>p. ej.: Completar una tarea compartida</x:v>
       </x:c>
       <x:c r="G143" s="2" t="str">
-        <x:v>z. B.: Die eigenen Gefühle gestehen lassen</x:v>
+        <x:v>z. B.: Eine gemeinsame Aufgabe erledigen</x:v>
       </x:c>
       <x:c r="H143" s="2" t="str">
         <x:v>V39 translated core chat + scenario</x:v>
@@ -4668,16 +4664,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D145" s="2" t="str">
-        <x:v>ex : Il a peur d'être rejeté</x:v>
+        <x:v>ex : Un malentendu complique la situation</x:v>
       </x:c>
       <x:c r="E145" s="2" t="str">
-        <x:v>e.g.: They're afraid of being rejected</x:v>
+        <x:v>e.g. A misunderstanding complicates the situation</x:v>
       </x:c>
       <x:c r="F145" s="2" t="str">
-        <x:v>p. ej.: Tiene miedo al rechazo</x:v>
+        <x:v>p. ej.: Un malentendido complica la situación</x:v>
       </x:c>
       <x:c r="G145" s="2" t="str">
-        <x:v>z. B.: Angst vor Zurückweisung</x:v>
+        <x:v>z. B.: Ein Missverständnis erschwert die Situation</x:v>
       </x:c>
       <x:c r="H145" s="2" t="str">
         <x:v>V39 translated core chat + scenario</x:v>
@@ -4728,16 +4724,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D147" s="2" t="str">
-        <x:v>Il pleut depuis des heures. La lumière vacille. Le silence entre vous dit tout ce que les mots n'osent pas.</x:v>
+        <x:v>Ajoute le contexte, l’ambiance ou les contraintes utiles…</x:v>
       </x:c>
       <x:c r="E147" s="2" t="str">
-        <x:v>It's been raining for hours. The light flickers. The silence between you says everything words dare not.</x:v>
+        <x:v>Add useful context, atmosphere or constraints…</x:v>
       </x:c>
       <x:c r="F147" s="2" t="str">
-        <x:v>Lleva horas lloviendo. La luz parpadea. El silencio entre ustedes lo dice todo, aunque las palabras no se atrevan.</x:v>
+        <x:v>Añade contexto, ambiente o restricciones útiles…</x:v>
       </x:c>
       <x:c r="G147" s="2" t="str">
-        <x:v>Seit Stunden regnet es. Das Licht flackert. Die Stille zwischen euch sagt alles, was Worte nicht auszusprechen wagen.</x:v>
+        <x:v>Füge nützlichen Kontext, Atmosphäre oder Einschränkungen hinzu…</x:v>
       </x:c>
       <x:c r="H147" s="2" t="str">
         <x:v>V39 translated core chat + scenario</x:v>
@@ -5688,16 +5684,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D179" s="3" t="str">
-        <x:v>ex : a woman sitting in a cozy library, warm light</x:v>
+        <x:v>ex : character in a quiet room, soft natural light</x:v>
       </x:c>
       <x:c r="E179" s="3" t="str">
-        <x:v>e.g.: a woman sitting in a cozy library, warm light</x:v>
+        <x:v>e.g. character in a quiet room, soft natural light</x:v>
       </x:c>
       <x:c r="F179" s="3" t="str">
-        <x:v>e.g.: a woman sitting in a cozy library, warm light</x:v>
+        <x:v>p. ej.: character in a quiet room, soft natural light</x:v>
       </x:c>
       <x:c r="G179" s="3" t="str">
-        <x:v>e.g.: a woman sitting in a cozy library, warm light</x:v>
+        <x:v>z. B.: character in a quiet room, soft natural light</x:v>
       </x:c>
       <x:c r="H179" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -5748,16 +5744,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D181" s="3" t="str">
-        <x:v>blurry, low quality…</x:v>
+        <x:v>ex : blurry, low quality, distorted…</x:v>
       </x:c>
       <x:c r="E181" s="3" t="str">
-        <x:v>blurry, low quality…</x:v>
+        <x:v>e.g. blurry, low quality, distorted…</x:v>
       </x:c>
       <x:c r="F181" s="3" t="str">
-        <x:v>blurry, low quality…</x:v>
+        <x:v>p. ej.: blurry, low quality, distorted…</x:v>
       </x:c>
       <x:c r="G181" s="3" t="str">
-        <x:v>blurry, low quality…</x:v>
+        <x:v>z. B.: blurry, low quality, distorted…</x:v>
       </x:c>
       <x:c r="H181" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -6018,16 +6014,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D190" s="3" t="str">
-        <x:v>ex : E:\STM\Data\Packages\ComfyUI\models</x:v>
+        <x:v>ex : C:\AI\ComfyUI\models</x:v>
       </x:c>
       <x:c r="E190" s="3" t="str">
-        <x:v>e.g.: E:\STM\Data\Packages\ComfyUI\models</x:v>
+        <x:v>e.g. C:\AI\ComfyUI\models</x:v>
       </x:c>
       <x:c r="F190" s="3" t="str">
-        <x:v>e.g.: E:\STM\Data\Packages\ComfyUI\models</x:v>
+        <x:v>p. ej.: C:\AI\ComfyUI\models</x:v>
       </x:c>
       <x:c r="G190" s="3" t="str">
-        <x:v>e.g.: E:\STM\Data\Packages\ComfyUI\models</x:v>
+        <x:v>z. B.: C:\AI\ComfyUI\models</x:v>
       </x:c>
       <x:c r="H190" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -6438,16 +6434,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D204" s="3" t="str">
-        <x:v>Rechercher…</x:v>
+        <x:v>Rechercher un dossier ou un modèle…</x:v>
       </x:c>
       <x:c r="E204" s="3" t="str">
-        <x:v>Search…</x:v>
+        <x:v>Search for a folder or model…</x:v>
       </x:c>
       <x:c r="F204" s="3" t="str">
-        <x:v>Search…</x:v>
+        <x:v>Buscar una carpeta o modelo…</x:v>
       </x:c>
       <x:c r="G204" s="3" t="str">
-        <x:v>Search…</x:v>
+        <x:v>Ordner oder Modell suchen…</x:v>
       </x:c>
       <x:c r="H204" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -7218,16 +7214,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D230" s="3" t="str">
-        <x:v>ex : detail_slider.safetensors</x:v>
+        <x:v>ex : example_style.safetensors</x:v>
       </x:c>
       <x:c r="E230" s="3" t="str">
-        <x:v>e.g.: detail_slider.safetensors</x:v>
+        <x:v>e.g. example_style.safetensors</x:v>
       </x:c>
       <x:c r="F230" s="3" t="str">
-        <x:v>e.g.: detail_slider.safetensors</x:v>
+        <x:v>p. ej.: example_style.safetensors</x:v>
       </x:c>
       <x:c r="G230" s="3" t="str">
-        <x:v>e.g.: detail_slider.safetensors</x:v>
+        <x:v>z. B.: example_style.safetensors</x:v>
       </x:c>
       <x:c r="H230" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -7278,16 +7274,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D232" s="3" t="str">
-        <x:v>ex : detailed</x:v>
+        <x:v>ex : style_token</x:v>
       </x:c>
       <x:c r="E232" s="3" t="str">
-        <x:v>e.g.: detailed</x:v>
+        <x:v>e.g. style_token</x:v>
       </x:c>
       <x:c r="F232" s="3" t="str">
-        <x:v>e.g.: detailed</x:v>
+        <x:v>p. ej.: style_token</x:v>
       </x:c>
       <x:c r="G232" s="3" t="str">
-        <x:v>e.g.: detailed</x:v>
+        <x:v>z. B.: style_token</x:v>
       </x:c>
       <x:c r="H232" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -7548,16 +7544,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D241" s="3" t="str">
-        <x:v>Contexte d'usage, style…</x:v>
+        <x:v>Ajoute une note d’utilisation facultative…</x:v>
       </x:c>
       <x:c r="E241" s="3" t="str">
-        <x:v>Usage context, style…</x:v>
+        <x:v>Add an optional usage note…</x:v>
       </x:c>
       <x:c r="F241" s="3" t="str">
-        <x:v>Usage context, style…</x:v>
+        <x:v>Añade una nota de uso opcional…</x:v>
       </x:c>
       <x:c r="G241" s="3" t="str">
-        <x:v>Usage context, style…</x:v>
+        <x:v>Optionale Nutzungshinweise hinzufügen…</x:v>
       </x:c>
       <x:c r="H241" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -7698,16 +7694,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D246" s="3" t="str">
-        <x:v>🔍 Rechercher…</x:v>
+        <x:v>Rechercher un LoRA…</x:v>
       </x:c>
       <x:c r="E246" s="3" t="str">
-        <x:v>🔍 Search…</x:v>
+        <x:v>Search LoRAs…</x:v>
       </x:c>
       <x:c r="F246" s="3" t="str">
-        <x:v>🔍 Search…</x:v>
+        <x:v>Buscar LoRAs…</x:v>
       </x:c>
       <x:c r="G246" s="3" t="str">
-        <x:v>🔍 Search…</x:v>
+        <x:v>LoRAs suchen…</x:v>
       </x:c>
       <x:c r="H246" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -9932,16 +9928,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D321" s="4" t="str">
-        <x:v>ex : Alex</x:v>
+        <x:v>Nom de l’utilisateur</x:v>
       </x:c>
       <x:c r="E321" s="4" t="str">
-        <x:v>e.g.: Alex</x:v>
+        <x:v>User name</x:v>
       </x:c>
       <x:c r="F321" s="4" t="str">
-        <x:v>e.g.: Alex</x:v>
+        <x:v>Nombre del usuario</x:v>
       </x:c>
       <x:c r="G321" s="4" t="str">
-        <x:v>e.g.: Alex</x:v>
+        <x:v>Benutzername</x:v>
       </x:c>
       <x:c r="H321" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -9992,16 +9988,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D323" s="4" t="str">
-        <x:v>ex : un photographe de 30 ans, cheveux bruns…</x:v>
+        <x:v>ex : adulte, tempérament calme, tenue décontractée…</x:v>
       </x:c>
       <x:c r="E323" s="4" t="str">
-        <x:v>e.g.: a 30-year-old photographer, brown hair…</x:v>
+        <x:v>e.g. adult, calm temperament, casual style…</x:v>
       </x:c>
       <x:c r="F323" s="4" t="str">
-        <x:v>e.g.: a 30-year-old photographer, brown hair…</x:v>
+        <x:v>p. ej.: persona adulta, temperamento tranquilo, estilo informal…</x:v>
       </x:c>
       <x:c r="G323" s="4" t="str">
-        <x:v>e.g.: a 30-year-old photographer, brown hair…</x:v>
+        <x:v>z. B.: erwachsene Person, ruhiges Temperament, legere Kleidung…</x:v>
       </x:c>
       <x:c r="H323" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -13262,16 +13258,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D432" s="3" t="str">
-        <x:v>— choisir —</x:v>
+        <x:v>— sélectionner —</x:v>
       </x:c>
       <x:c r="E432" s="3" t="str">
-        <x:v>— choose —</x:v>
+        <x:v>— select —</x:v>
       </x:c>
       <x:c r="F432" s="3" t="str">
-        <x:v>— choose —</x:v>
+        <x:v>— seleccionar —</x:v>
       </x:c>
       <x:c r="G432" s="3" t="str">
-        <x:v>— choose —</x:v>
+        <x:v>— auswählen —</x:v>
       </x:c>
       <x:c r="H432" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -15938,16 +15934,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D516" t="str">
-        <x:v>Ex : Léa</x:v>
+        <x:v>Nom du personnage</x:v>
       </x:c>
       <x:c r="E516" t="str">
-        <x:v>e.g.: Léa</x:v>
+        <x:v>Character name</x:v>
       </x:c>
       <x:c r="F516" t="str">
-        <x:v>Ej.: Léa</x:v>
+        <x:v>Nombre del personaje</x:v>
       </x:c>
       <x:c r="G516" t="str">
-        <x:v>z. B.: Léa</x:v>
+        <x:v>Charaktername</x:v>
       </x:c>
       <x:c r="H516" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -16002,16 +15998,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D518" t="str">
-        <x:v>Vous vous êtes rencontrés…</x:v>
+        <x:v>Décris comment les personnages se sont rencontrés…</x:v>
       </x:c>
       <x:c r="E518" t="str">
-        <x:v>How you met…</x:v>
+        <x:v>Describe how the characters met…</x:v>
       </x:c>
       <x:c r="F518" t="str">
-        <x:v>Cómo se conocieron…</x:v>
+        <x:v>Describe cómo se conocieron los personajes…</x:v>
       </x:c>
       <x:c r="G518" t="str">
-        <x:v>Wie ihr euch kennengelernt habt…</x:v>
+        <x:v>Beschreibe, wie sich die Charaktere kennengelernt haben…</x:v>
       </x:c>
       <x:c r="H518" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -16162,16 +16158,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D523" t="str">
-        <x:v>Curieuse, chaleureuse…</x:v>
+        <x:v>ex : curieux, patient, direct…</x:v>
       </x:c>
       <x:c r="E523" t="str">
-        <x:v>Curious, warm…</x:v>
+        <x:v>e.g. curious, patient, direct…</x:v>
       </x:c>
       <x:c r="F523" t="str">
-        <x:v>Curiosa, cálida…</x:v>
+        <x:v>p. ej.: curioso, paciente, directo…</x:v>
       </x:c>
       <x:c r="G523" t="str">
-        <x:v>Neugierig, warmherzig…</x:v>
+        <x:v>z. B.: neugierig, geduldig, direkt…</x:v>
       </x:c>
       <x:c r="H523" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -16610,16 +16606,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D537" t="str">
-        <x:v>Ex. : 25</x:v>
+        <x:v>ex : 30</x:v>
       </x:c>
       <x:c r="E537" t="str">
-        <x:v>e.g. 25</x:v>
+        <x:v>e.g. 30</x:v>
       </x:c>
       <x:c r="F537" t="str">
-        <x:v>p. ej. 25</x:v>
+        <x:v>p. ej.: 30</x:v>
       </x:c>
       <x:c r="G537" t="str">
-        <x:v>z. B. 25</x:v>
+        <x:v>z. B.: 30</x:v>
       </x:c>
       <x:c r="H537" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -16706,16 +16702,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D540" t="str">
-        <x:v>Cheveux bruns, yeux verts…</x:v>
+        <x:v>ex : cheveux courts, tenue décontractée…</x:v>
       </x:c>
       <x:c r="E540" t="str">
-        <x:v>Brown hair, green eyes…</x:v>
+        <x:v>e.g. short hair, casual clothes…</x:v>
       </x:c>
       <x:c r="F540" t="str">
-        <x:v>Cabello castaño, ojos verdes…</x:v>
+        <x:v>p. ej.: pelo corto, ropa informal…</x:v>
       </x:c>
       <x:c r="G540" t="str">
-        <x:v>Braunes Haar, grüne Augen…</x:v>
+        <x:v>z. B.: kurze Haare, legere Kleidung…</x:v>
       </x:c>
       <x:c r="H540" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -16834,16 +16830,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D544" t="str">
-        <x:v>Bonjour !</x:v>
+        <x:v>Écris un premier message…</x:v>
       </x:c>
       <x:c r="E544" t="str">
-        <x:v>Hello!</x:v>
+        <x:v>Write an opening message…</x:v>
       </x:c>
       <x:c r="F544" t="str">
-        <x:v>¡Hola!</x:v>
+        <x:v>Escribe un primer mensaje…</x:v>
       </x:c>
       <x:c r="G544" t="str">
-        <x:v>Hallo!</x:v>
+        <x:v>Schreibe eine erste Nachricht…</x:v>
       </x:c>
       <x:c r="H544" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -17282,16 +17278,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D558" t="str">
-        <x:v>décris en anglais…</x:v>
+        <x:v>Décris la configuration en anglais…</x:v>
       </x:c>
       <x:c r="E558" t="str">
-        <x:v>describe in English…</x:v>
+        <x:v>Describe the configuration in English…</x:v>
       </x:c>
       <x:c r="F558" t="str">
-        <x:v>descríbelo en inglés…</x:v>
+        <x:v>Describe la configuración en inglés…</x:v>
       </x:c>
       <x:c r="G558" t="str">
-        <x:v>auf Englisch beschreiben…</x:v>
+        <x:v>Konfiguration auf Englisch beschreiben…</x:v>
       </x:c>
       <x:c r="H558" t="str">
         <x:v>Runtime UI string added in v38.1.0</x:v>
@@ -23210,16 +23206,16 @@
         <x:v>placeholder</x:v>
       </x:c>
       <x:c r="D743" s="28" t="str">
-        <x:v>Lieu personnalisé</x:v>
+        <x:v>Saisis un lieu personnalisé…</x:v>
       </x:c>
       <x:c r="E743" s="28" t="str">
-        <x:v>Custom place</x:v>
+        <x:v>Enter a custom place…</x:v>
       </x:c>
       <x:c r="F743" s="28" t="str">
-        <x:v>Lugar personalizado</x:v>
+        <x:v>Introduce un lugar personalizado…</x:v>
       </x:c>
       <x:c r="G743" s="28" t="str">
-        <x:v>Eigener Ort</x:v>
+        <x:v>Eigenen Ort eingeben…</x:v>
       </x:c>
       <x:c r="H743" s="28" t="str">
         <x:v>V39 scenario selector</x:v>
@@ -28106,16 +28102,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D896" s="28" t="str">
-        <x:v>ex. ylisak</x:v>
+        <x:v>ex : character_token</x:v>
       </x:c>
       <x:c r="E896" s="28" t="str">
-        <x:v>e.g. ylisak</x:v>
+        <x:v>e.g. character_token</x:v>
       </x:c>
       <x:c r="F896" s="28" t="str">
-        <x:v>p. ej. ylisak</x:v>
+        <x:v>p. ej.: character_token</x:v>
       </x:c>
       <x:c r="G896" s="28" t="str">
-        <x:v>z. B. ylisak</x:v>
+        <x:v>z. B.: character_token</x:v>
       </x:c>
       <x:c r="H896" s="28" t="str">
         <x:v>Added by v39.1.0 non-destructive merge</x:v>
@@ -28202,16 +28198,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D899" s="28" t="str">
-        <x:v>Instruction personnalisée…</x:v>
+        <x:v>Saisis une instruction personnalisée…</x:v>
       </x:c>
       <x:c r="E899" s="28" t="str">
-        <x:v>Custom instruction…</x:v>
+        <x:v>Enter a custom instruction…</x:v>
       </x:c>
       <x:c r="F899" s="28" t="str">
-        <x:v>Instrucción personalizada…</x:v>
+        <x:v>Introduce una instrucción personalizada…</x:v>
       </x:c>
       <x:c r="G899" s="28" t="str">
-        <x:v>Eigene Anweisung…</x:v>
+        <x:v>Eigene Anweisung eingeben…</x:v>
       </x:c>
       <x:c r="H899" s="28" t="str">
         <x:v>Added by v39.1.0 non-destructive merge</x:v>
@@ -28874,7 +28870,7 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D920" t="str">
-        <x:v>Écris exactement les mots prononcés dans l'échantillon.</x:v>
+        <x:v>Écris exactement les mots prononcés dans l’échantillon.</x:v>
       </x:c>
       <x:c r="E920" t="str">
         <x:v>Write the exact words spoken in the sample.</x:v>
@@ -31114,16 +31110,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D990" t="str">
-        <x:v>trigger LoRA optionnel, ex : sebpersona</x:v>
+        <x:v>trigger LoRA optionnel, ex : user_token</x:v>
       </x:c>
       <x:c r="E990" t="str">
-        <x:v>optional LoRA trigger, ex: sebpersona</x:v>
+        <x:v>optional LoRA trigger, e.g. user_token</x:v>
       </x:c>
       <x:c r="F990" t="str">
-        <x:v>trigger LoRA opcional, ej.: sebpersona</x:v>
+        <x:v>trigger LoRA opcional, p. ej.: user_token</x:v>
       </x:c>
       <x:c r="G990" t="str">
-        <x:v>optionaler LoRA-Trigger, z. B. sebpersona</x:v>
+        <x:v>optionaler LoRA-Trigger, z. B.: user_token</x:v>
       </x:c>
       <x:c r="H990" t="str">
         <x:v>Recovered from verified runtime locales during v40.0.0 synchronization</x:v>
@@ -31647,7 +31643,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>40.0.4</x:v>
+        <x:v>40.0.6</x:v>
       </x:c>
     </x:row>
     <x:row r="6">

--- a/resources/i18n/translations_master.xlsx
+++ b/resources/i18n/translations_master.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rf93f165648e5486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="Rfffc0bd185a64a38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="R75ed1cf4f60449ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="R0081423c699c4660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rbf403f12b4fa4266"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="Rce210d1855b2474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="Rff3c0b422936442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="Rbc06c7a9d5474839"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8684,16 +8684,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D279" s="3" t="str">
-        <x:v>État des moteurs et contrôle des process. Vérifie ici si quelque chose coince.</x:v>
+        <x:v>État des moteurs et connexions API locales. Vérifiez ici si un service est indisponible.</x:v>
       </x:c>
       <x:c r="E279" s="3" t="str">
-        <x:v>Engine status and process control. Check here if something is stuck.</x:v>
+        <x:v>Engine status and local API connections. Check here if something is unavailable.</x:v>
       </x:c>
       <x:c r="F279" s="3" t="str">
-        <x:v>Engine status and process control. Check here if something is stuck.</x:v>
+        <x:v>Estado de los motores y conexiones API locales. Comprueba aquí si algún servicio no está disponible.</x:v>
       </x:c>
       <x:c r="G279" s="3" t="str">
-        <x:v>Engine status and process control. Check here if something is stuck.</x:v>
+        <x:v>Status der Engines und lokalen API-Verbindungen. Hier sehen Sie, ob ein Dienst nicht verfügbar ist.</x:v>
       </x:c>
       <x:c r="H279" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -8744,16 +8744,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D281" s="3" t="str">
-        <x:v>ComfyUI (moteur image)</x:v>
+        <x:v>ComfyUI tiers (moteur image)</x:v>
       </x:c>
       <x:c r="E281" s="3" t="str">
-        <x:v>ComfyUI (image engine)</x:v>
+        <x:v>External ComfyUI (image engine)</x:v>
       </x:c>
       <x:c r="F281" s="3" t="str">
-        <x:v>ComfyUI (image engine)</x:v>
+        <x:v>ComfyUI externo (motor de imagen)</x:v>
       </x:c>
       <x:c r="G281" s="3" t="str">
-        <x:v>ComfyUI (image engine)</x:v>
+        <x:v>Externes ComfyUI (Bild-Engine)</x:v>
       </x:c>
       <x:c r="H281" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -8765,7 +8765,7 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="3" t="str">
-        <x:v>system.comfy_start_btn</x:v>
+        <x:v>system.comfy_status_connected</x:v>
       </x:c>
       <x:c r="B282" s="3" t="str">
         <x:v>system</x:v>
@@ -8774,28 +8774,30 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D282" s="3" t="str">
-        <x:v>Démarrer</x:v>
+        <x:v>connecté</x:v>
       </x:c>
       <x:c r="E282" s="3" t="str">
-        <x:v>Start</x:v>
+        <x:v>connected</x:v>
       </x:c>
       <x:c r="F282" s="3" t="str">
-        <x:v>Start</x:v>
+        <x:v>conectado</x:v>
       </x:c>
       <x:c r="G282" s="3" t="str">
-        <x:v>Start</x:v>
+        <x:v>verbunden</x:v>
       </x:c>
       <x:c r="H282" s="3" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I282" s="3"/>
+        <x:v>v40.0.7 external ComfyUI only</x:v>
+      </x:c>
+      <x:c r="I282" s="3" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J282" s="3" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="3" t="str">
-        <x:v>system.comfy_restart_btn</x:v>
+        <x:v>system.comfy_status_offline</x:v>
       </x:c>
       <x:c r="B283" s="3" t="str">
         <x:v>system</x:v>
@@ -8804,84 +8806,70 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D283" s="3" t="str">
-        <x:v>Redémarrer</x:v>
+        <x:v>hors ligne — démarrez ComfyUI depuis son propre lanceur</x:v>
       </x:c>
       <x:c r="E283" s="3" t="str">
-        <x:v>Restart</x:v>
+        <x:v>offline — start ComfyUI from its own launcher</x:v>
       </x:c>
       <x:c r="F283" s="3" t="str">
-        <x:v>Restart</x:v>
+        <x:v>sin conexión — inicia ComfyUI desde su propio lanzador</x:v>
       </x:c>
       <x:c r="G283" s="3" t="str">
-        <x:v>Restart</x:v>
+        <x:v>offline — starten Sie ComfyUI über den eigenen Launcher</x:v>
       </x:c>
       <x:c r="H283" s="3" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I283" s="3"/>
+        <x:v>v40.0.7 external ComfyUI only</x:v>
+      </x:c>
+      <x:c r="I283" s="3" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J283" s="3" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="3" t="str">
-        <x:v>system.comfy_stop_btn</x:v>
+        <x:v>settings.comfy_url_label</x:v>
       </x:c>
       <x:c r="B284" s="3" t="str">
-        <x:v>system</x:v>
+        <x:v>settings</x:v>
       </x:c>
       <x:c r="C284" s="3" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="D284" s="3" t="str">
-        <x:v>Arrêter</x:v>
+        <x:v>Adresse API de ComfyUI</x:v>
       </x:c>
       <x:c r="E284" s="3" t="str">
-        <x:v>Stop</x:v>
+        <x:v>ComfyUI API address</x:v>
       </x:c>
       <x:c r="F284" s="3" t="str">
-        <x:v>Stop</x:v>
+        <x:v>Dirección API de ComfyUI</x:v>
       </x:c>
       <x:c r="G284" s="3" t="str">
-        <x:v>Stop</x:v>
+        <x:v>ComfyUI-API-Adresse</x:v>
       </x:c>
       <x:c r="H284" s="3" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I284" s="3"/>
+        <x:v>v40.0.7 external ComfyUI only</x:v>
+      </x:c>
+      <x:c r="I284" s="3" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J284" s="3" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
-      <x:c r="A285" s="3" t="str">
-        <x:v>system.comfy_kill_btn</x:v>
-      </x:c>
-      <x:c r="B285" s="3" t="str">
-        <x:v>system</x:v>
-      </x:c>
-      <x:c r="C285" s="3" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D285" s="3" t="str">
-        <x:v>Kill (process bloqué)</x:v>
-      </x:c>
-      <x:c r="E285" s="3" t="str">
-        <x:v>Kill (stuck process)</x:v>
-      </x:c>
-      <x:c r="F285" s="3" t="str">
-        <x:v>Kill (stuck process)</x:v>
-      </x:c>
-      <x:c r="G285" s="3" t="str">
-        <x:v>Kill (stuck process)</x:v>
-      </x:c>
-      <x:c r="H285" s="3" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
+      <x:c r="A285" s="3"/>
+      <x:c r="B285" s="3"/>
+      <x:c r="C285" s="3"/>
+      <x:c r="D285" s="3"/>
+      <x:c r="E285" s="3"/>
+      <x:c r="F285" s="3"/>
+      <x:c r="G285" s="3"/>
+      <x:c r="H285" s="3"/>
       <x:c r="I285" s="3"/>
-      <x:c r="J285" s="3" t="str">
-        <x:v>fallback_en</x:v>
-      </x:c>
+      <x:c r="J285" s="3"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="3" t="str">
@@ -8924,16 +8912,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D287" s="3" t="str">
-        <x:v>« Kill » force l'arrêt si ComfyUI est figé. « Libérer la VRAM » décharge ses modèles.</x:v>
+        <x:v>ComfyUI est une application tierce installée séparément. Démarrez, arrêtez ou redémarrez-la depuis son propre lanceur. AmiorAI peut uniquement demander le déchargement de ses modèles via l’API locale.</x:v>
       </x:c>
       <x:c r="E287" s="3" t="str">
-        <x:v>'Kill' forces stop if ComfyUI is frozen. 'Free VRAM' unloads its models.</x:v>
+        <x:v>ComfyUI is a separately installed third-party application. Start, stop or restart it from its own launcher. AmiorAI can only request model unloading through the local API.</x:v>
       </x:c>
       <x:c r="F287" s="3" t="str">
-        <x:v>'Kill' forces stop if ComfyUI is frozen. 'Free VRAM' unloads its models.</x:v>
+        <x:v>ComfyUI es una aplicación de terceros instalada por separado. Iníciala, detenla o reiníciala desde su propio lanzador. AmiorAI solo puede solicitar la descarga de modelos mediante la API local.</x:v>
       </x:c>
       <x:c r="G287" s="3" t="str">
-        <x:v>'Kill' forces stop if ComfyUI is frozen. 'Free VRAM' unloads its models.</x:v>
+        <x:v>ComfyUI ist eine separat installierte Drittanbieter-Anwendung. Starten, stoppen oder starten Sie sie über ihren eigenen Launcher neu. AmiorAI kann über die lokale API nur das Entladen der Modelle anfordern.</x:v>
       </x:c>
       <x:c r="H287" s="3" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -11050,23 +11038,25 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D358" s="4" t="str">
-        <x:v>Connexion ComfyUI</x:v>
+        <x:v>Connexion ComfyUI tiers</x:v>
       </x:c>
       <x:c r="E358" s="4" t="str">
-        <x:v>ComfyUI connection</x:v>
+        <x:v>External ComfyUI connection</x:v>
       </x:c>
       <x:c r="F358" s="4" t="str">
-        <x:v>ComfyUI connection</x:v>
+        <x:v>Conexión con ComfyUI externo</x:v>
       </x:c>
       <x:c r="G358" s="4" t="str">
-        <x:v>ComfyUI connection</x:v>
+        <x:v>Verbindung zu externem ComfyUI</x:v>
       </x:c>
       <x:c r="H358" s="4" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I358" s="4"/>
+        <x:v>v40.0.7 external ComfyUI only</x:v>
+      </x:c>
+      <x:c r="I358" s="4" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J358" s="4" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="359">
@@ -11080,23 +11070,25 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D359" s="4" t="str">
-        <x:v>Le choix des modèles (UNet/Checkpoint/CLIP/VAE) et des workflows par famille se fait maintenant dans l'onglet &lt;strong&gt;Studio Image&lt;/strong&gt; — ici, uniquement la connexion au moteur ComfyUI lui-même.</x:v>
+        <x:v>AmiorAI se connecte uniquement à une installation ComfyUI tierce déjà démarrée. Il n’installe, ne lance, ne redémarre et n’arrête jamais ComfyUI. Les modèles et workflows se choisissent dans &lt;strong&gt;Studio Image&lt;/strong&gt;.</x:v>
       </x:c>
       <x:c r="E359" s="4" t="str">
-        <x:v>Model selection (UNet/Checkpoint/CLIP/VAE) and workflows per family is now in the &lt;strong&gt;Image Studio&lt;/strong&gt; tab — here, only the ComfyUI engine connection.</x:v>
+        <x:v>AmiorAI only connects to an already running third-party ComfyUI installation. It never installs, launches, restarts or stops ComfyUI. Image models and workflows are selected in &lt;strong&gt;Image Studio&lt;/strong&gt;.</x:v>
       </x:c>
       <x:c r="F359" s="4" t="str">
-        <x:v>Model selection (UNet/Checkpoint/CLIP/VAE) and workflows per family is now in the &lt;strong&gt;Image Studio&lt;/strong&gt; tab — here, only the ComfyUI engine connection.</x:v>
+        <x:v>AmiorAI solo se conecta a una instalación de ComfyUI de terceros que ya esté en ejecución. Nunca instala, inicia, reinicia ni detiene ComfyUI. Los modelos y flujos de trabajo se eligen en &lt;strong&gt;Estudio de imágenes&lt;/strong&gt;.</x:v>
       </x:c>
       <x:c r="G359" s="4" t="str">
-        <x:v>Model selection (UNet/Checkpoint/CLIP/VAE) and workflows per family is now in the &lt;strong&gt;Image Studio&lt;/strong&gt; tab — here, only the ComfyUI engine connection.</x:v>
+        <x:v>AmiorAI verbindet sich nur mit einer bereits laufenden ComfyUI-Installation eines Drittanbieters. ComfyUI wird niemals von AmiorAI installiert, gestartet, neu gestartet oder beendet. Modelle und Workflows werden in &lt;strong&gt;Image Studio&lt;/strong&gt; ausgewählt.</x:v>
       </x:c>
       <x:c r="H359" s="4" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I359" s="4"/>
+        <x:v>v40.0.7 external ComfyUI only</x:v>
+      </x:c>
+      <x:c r="I359" s="4" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J359" s="4" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -31643,7 +31635,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>40.0.6</x:v>
+        <x:v>40.0.7</x:v>
       </x:c>
     </x:row>
     <x:row r="6">

--- a/resources/i18n/translations_master.xlsx
+++ b/resources/i18n/translations_master.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rbf403f12b4fa4266"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="Rce210d1855b2474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="Rff3c0b422936442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="Rbc06c7a9d5474839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rf74d86803f6b498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="R2d542a0dca5449c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="Rbeb30cfa7bf74f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="R43e0dd6599bb4457"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -886,19 +886,23 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>📥 Importer un personnage (JSON)</x:v>
+        <x:v>📥 Importer un personnage partagé</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>📥 Import a character (JSON)</x:v>
+        <x:v>📥 Import shared character</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>📥 Importar un personaje (JSON)</x:v>
+        <x:v>📥 Importar personaje compartido</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>📥 Charakter importieren (JSON)</x:v>
-      </x:c>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
+        <x:v>📥 Geteilten Charakter importieren</x:v>
+      </x:c>
+      <x:c r="H17" s="4" t="str">
+        <x:v>Updated by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I17" s="4" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J17" s="4" t="str">
         <x:v>ok</x:v>
       </x:c>
@@ -3244,23 +3248,25 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
-        <x:v>Exporter ce personnage (JSON + historique)</x:v>
+        <x:v>Exporter le paquet partageable (fiche + avatar + visages d’humeur)</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>Export this character (JSON + history)</x:v>
+        <x:v>Export share package (profile + avatar + mood faces)</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
-        <x:v>Export this character (JSON + history)</x:v>
+        <x:v>Exportar paquete compartible (ficha + avatar + rostros de ánimo)</x:v>
       </x:c>
       <x:c r="G97" s="4" t="str">
-        <x:v>Export this character (JSON + history)</x:v>
+        <x:v>Teilbares Paket exportieren (Profil + Avatar + Stimmungsbilder)</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I97" s="4"/>
+        <x:v>Updated by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I97" s="4" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J97" s="4" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -30942,19 +30948,19 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D985" t="str">
-        <x:v>40.0.4</x:v>
+        <x:v>40.0.8</x:v>
       </x:c>
       <x:c r="E985" t="str">
-        <x:v>40.0.4</x:v>
+        <x:v>40.0.8</x:v>
       </x:c>
       <x:c r="F985" t="str">
-        <x:v>40.0.4</x:v>
+        <x:v>40.0.8</x:v>
       </x:c>
       <x:c r="G985" t="str">
-        <x:v>40.0.4</x:v>
+        <x:v>40.0.8</x:v>
       </x:c>
       <x:c r="H985" t="str">
-        <x:v>Updated by v40.0.4 GitHub licence and copyright patch</x:v>
+        <x:v>Updated by v40.0.8 public share packages</x:v>
       </x:c>
       <x:c r="I985" t="str">
         <x:v>resources/i18n/locales/*.json</x:v>
@@ -31280,6 +31286,358 @@
         <x:v>resources/i18n/locales/*.json</x:v>
       </x:c>
       <x:c r="J995" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996">
+      <x:c r="A996" t="str">
+        <x:v>scenario.import_btn</x:v>
+      </x:c>
+      <x:c r="B996" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C996" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D996" t="str">
+        <x:v>📥 Importer un scénario partagé</x:v>
+      </x:c>
+      <x:c r="E996" t="str">
+        <x:v>📥 Import shared scenario</x:v>
+      </x:c>
+      <x:c r="F996" t="str">
+        <x:v>📥 Importar escenario compartido</x:v>
+      </x:c>
+      <x:c r="G996" t="str">
+        <x:v>📥 Geteiltes Szenario importieren</x:v>
+      </x:c>
+      <x:c r="H996" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I996" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J996" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997">
+      <x:c r="A997" t="str">
+        <x:v>scenario.share_hint</x:v>
+      </x:c>
+      <x:c r="B997" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C997" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D997" t="str">
+        <x:v>Les paquets de scénario partagés contiennent uniquement les données narratives.</x:v>
+      </x:c>
+      <x:c r="E997" t="str">
+        <x:v>Shared scenario packages contain narrative data only.</x:v>
+      </x:c>
+      <x:c r="F997" t="str">
+        <x:v>Los paquetes de escenario compartidos solo contienen datos narrativos.</x:v>
+      </x:c>
+      <x:c r="G997" t="str">
+        <x:v>Geteilte Szenariopakete enthalten ausschließlich narrative Daten.</x:v>
+      </x:c>
+      <x:c r="H997" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I997" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J997" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998">
+      <x:c r="A998" t="str">
+        <x:v>scenario.export_btn</x:v>
+      </x:c>
+      <x:c r="B998" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C998" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D998" t="str">
+        <x:v>📤 Partager</x:v>
+      </x:c>
+      <x:c r="E998" t="str">
+        <x:v>📤 Share</x:v>
+      </x:c>
+      <x:c r="F998" t="str">
+        <x:v>📤 Compartir</x:v>
+      </x:c>
+      <x:c r="G998" t="str">
+        <x:v>📤 Teilen</x:v>
+      </x:c>
+      <x:c r="H998" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I998" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J998" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999">
+      <x:c r="A999" t="str">
+        <x:v>scenario.edit_btn</x:v>
+      </x:c>
+      <x:c r="B999" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C999" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D999" t="str">
+        <x:v>✏️ Modifier</x:v>
+      </x:c>
+      <x:c r="E999" t="str">
+        <x:v>✏️ Edit</x:v>
+      </x:c>
+      <x:c r="F999" t="str">
+        <x:v>✏️ Editar</x:v>
+      </x:c>
+      <x:c r="G999" t="str">
+        <x:v>✏️ Bearbeiten</x:v>
+      </x:c>
+      <x:c r="H999" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I999" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J999" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000">
+      <x:c r="A1000" t="str">
+        <x:v>scenario.delete_confirm</x:v>
+      </x:c>
+      <x:c r="B1000" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C1000" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1000" t="str">
+        <x:v>Supprimer ce scénario ?</x:v>
+      </x:c>
+      <x:c r="E1000" t="str">
+        <x:v>Delete this scenario?</x:v>
+      </x:c>
+      <x:c r="F1000" t="str">
+        <x:v>¿Eliminar este escenario?</x:v>
+      </x:c>
+      <x:c r="G1000" t="str">
+        <x:v>Dieses Szenario löschen?</x:v>
+      </x:c>
+      <x:c r="H1000" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1000" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1000" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" t="str">
+        <x:v>scenario.apply_title</x:v>
+      </x:c>
+      <x:c r="B1001" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C1001" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1001" t="str">
+        <x:v>Appliquer à la conversation active</x:v>
+      </x:c>
+      <x:c r="E1001" t="str">
+        <x:v>Apply to active conversation</x:v>
+      </x:c>
+      <x:c r="F1001" t="str">
+        <x:v>Aplicar a la conversación activa</x:v>
+      </x:c>
+      <x:c r="G1001" t="str">
+        <x:v>Auf die aktive Unterhaltung anwenden</x:v>
+      </x:c>
+      <x:c r="H1001" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1001" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1001" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002">
+      <x:c r="A1002" t="str">
+        <x:v>scenario.apply_btn</x:v>
+      </x:c>
+      <x:c r="B1002" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C1002" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1002" t="str">
+        <x:v>▶ Appliquer</x:v>
+      </x:c>
+      <x:c r="E1002" t="str">
+        <x:v>▶ Apply</x:v>
+      </x:c>
+      <x:c r="F1002" t="str">
+        <x:v>▶ Aplicar</x:v>
+      </x:c>
+      <x:c r="G1002" t="str">
+        <x:v>▶ Anwenden</x:v>
+      </x:c>
+      <x:c r="H1002" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1002" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1002" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003">
+      <x:c r="A1003" t="str">
+        <x:v>scenario.import_success</x:v>
+      </x:c>
+      <x:c r="B1003" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C1003" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1003" t="str">
+        <x:v>Scénario « {title} » importé !</x:v>
+      </x:c>
+      <x:c r="E1003" t="str">
+        <x:v>Scenario “{title}” imported!</x:v>
+      </x:c>
+      <x:c r="F1003" t="str">
+        <x:v>¡Escenario «{title}» importado!</x:v>
+      </x:c>
+      <x:c r="G1003" t="str">
+        <x:v>Szenario „{title}“ importiert!</x:v>
+      </x:c>
+      <x:c r="H1003" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1003" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1003" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004">
+      <x:c r="A1004" t="str">
+        <x:v>scenario.import_failed</x:v>
+      </x:c>
+      <x:c r="B1004" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C1004" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1004" t="str">
+        <x:v>Échec de l’import du scénario : {error}</x:v>
+      </x:c>
+      <x:c r="E1004" t="str">
+        <x:v>Scenario import failed: {error}</x:v>
+      </x:c>
+      <x:c r="F1004" t="str">
+        <x:v>Error al importar el escenario: {error}</x:v>
+      </x:c>
+      <x:c r="G1004" t="str">
+        <x:v>Szenarioimport fehlgeschlagen: {error}</x:v>
+      </x:c>
+      <x:c r="H1004" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1004" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1004" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005">
+      <x:c r="A1005" t="str">
+        <x:v>char.share_hint</x:v>
+      </x:c>
+      <x:c r="B1005" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1005" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1005" t="str">
+        <x:v>Paquet public : les conversations, mémoires personnelles, voix et réglages ne sont jamais inclus.</x:v>
+      </x:c>
+      <x:c r="E1005" t="str">
+        <x:v>Public package: conversations, personal memories, voice and settings are never included.</x:v>
+      </x:c>
+      <x:c r="F1005" t="str">
+        <x:v>Paquete público: nunca se incluyen conversaciones, recuerdos personales, voz ni ajustes.</x:v>
+      </x:c>
+      <x:c r="G1005" t="str">
+        <x:v>Öffentliches Paket: Unterhaltungen, persönliche Erinnerungen, Stimme und Einstellungen werden niemals eingeschlossen.</x:v>
+      </x:c>
+      <x:c r="H1005" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1005" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1005" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006">
+      <x:c r="A1006" t="str">
+        <x:v>char.share_btn</x:v>
+      </x:c>
+      <x:c r="B1006" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1006" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1006" t="str">
+        <x:v>📤 Partager</x:v>
+      </x:c>
+      <x:c r="E1006" t="str">
+        <x:v>📤 Share</x:v>
+      </x:c>
+      <x:c r="F1006" t="str">
+        <x:v>📤 Compartir</x:v>
+      </x:c>
+      <x:c r="G1006" t="str">
+        <x:v>📤 Teilen</x:v>
+      </x:c>
+      <x:c r="H1006" t="str">
+        <x:v>Added by v40.0.8 public share packages</x:v>
+      </x:c>
+      <x:c r="I1006" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1006" t="str">
         <x:v>ok</x:v>
       </x:c>
     </x:row>

--- a/resources/i18n/translations_master.xlsx
+++ b/resources/i18n/translations_master.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rf74d86803f6b498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="R2d542a0dca5449c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="Rbeb30cfa7bf74f2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="R43e0dd6599bb4457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="R1f966a4abed0466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="R4994c2dd9be74e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="Rc372d3b3e4ba421a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="Rda33240f16e94c9c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30948,19 +30948,19 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D985" t="str">
-        <x:v>40.0.8</x:v>
+        <x:v>40.0.9</x:v>
       </x:c>
       <x:c r="E985" t="str">
-        <x:v>40.0.8</x:v>
+        <x:v>40.0.9</x:v>
       </x:c>
       <x:c r="F985" t="str">
-        <x:v>40.0.8</x:v>
+        <x:v>40.0.9</x:v>
       </x:c>
       <x:c r="G985" t="str">
-        <x:v>40.0.8</x:v>
+        <x:v>40.0.9</x:v>
       </x:c>
       <x:c r="H985" t="str">
-        <x:v>Updated by v40.0.8 public share packages</x:v>
+        <x:v>Updated by v40.0.9 visual creators</x:v>
       </x:c>
       <x:c r="I985" t="str">
         <x:v>resources/i18n/locales/*.json</x:v>
@@ -31638,6 +31638,294 @@
         <x:v>resources/i18n/locales/*.json</x:v>
       </x:c>
       <x:c r="J1006" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007">
+      <x:c r="A1007" s="28" t="str">
+        <x:v>char.visual_style.title</x:v>
+      </x:c>
+      <x:c r="B1007" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1007" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1007" s="28" t="str">
+        <x:v>Choisir un créateur visuel</x:v>
+      </x:c>
+      <x:c r="E1007" s="28" t="str">
+        <x:v>Choose a visual creator</x:v>
+      </x:c>
+      <x:c r="F1007" s="28" t="str">
+        <x:v>Elige un creador visual</x:v>
+      </x:c>
+      <x:c r="G1007" s="28" t="str">
+        <x:v>Visuellen Ersteller auswählen</x:v>
+      </x:c>
+      <x:c r="H1007" s="28" t="str">
+        <x:v>Added by v40.0.9 isolated realistic/anime/cartoon creators</x:v>
+      </x:c>
+      <x:c r="I1007" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1007" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008">
+      <x:c r="A1008" s="28" t="str">
+        <x:v>char.visual_style.hint</x:v>
+      </x:c>
+      <x:c r="B1008" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1008" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1008" s="28" t="str">
+        <x:v>Chaque créateur conserve son propre brouillon et sa propre bibliothèque d’aperçus.</x:v>
+      </x:c>
+      <x:c r="E1008" s="28" t="str">
+        <x:v>Each creator keeps its own draft and its own preview library.</x:v>
+      </x:c>
+      <x:c r="F1008" s="28" t="str">
+        <x:v>Cada creador conserva su propio borrador y su propia biblioteca de vistas previas.</x:v>
+      </x:c>
+      <x:c r="G1008" s="28" t="str">
+        <x:v>Jeder Ersteller behält seinen eigenen Entwurf und seine eigene Vorschaubibliothek.</x:v>
+      </x:c>
+      <x:c r="H1008" s="28" t="str">
+        <x:v>Added by v40.0.9 isolated realistic/anime/cartoon creators</x:v>
+      </x:c>
+      <x:c r="I1008" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1008" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009">
+      <x:c r="A1009" s="28" t="str">
+        <x:v>char.visual_style.realistic_title</x:v>
+      </x:c>
+      <x:c r="B1009" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1009" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1009" s="28" t="str">
+        <x:v>Créateur réaliste</x:v>
+      </x:c>
+      <x:c r="E1009" s="28" t="str">
+        <x:v>Realistic creator</x:v>
+      </x:c>
+      <x:c r="F1009" s="28" t="str">
+        <x:v>Creador realista</x:v>
+      </x:c>
+      <x:c r="G1009" s="28" t="str">
+        <x:v>Realistischer Ersteller</x:v>
+      </x:c>
+      <x:c r="H1009" s="28" t="str">
+        <x:v>Added by v40.0.9 visual style</x:v>
+      </x:c>
+      <x:c r="I1009" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1009" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010">
+      <x:c r="A1010" s="28" t="str">
+        <x:v>char.visual_style.realistic_desc</x:v>
+      </x:c>
+      <x:c r="B1010" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1010" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1010" s="28" t="str">
+        <x:v>Génération photoréaliste actuelle, sans changement.</x:v>
+      </x:c>
+      <x:c r="E1010" s="28" t="str">
+        <x:v>Current photorealistic generation, unchanged.</x:v>
+      </x:c>
+      <x:c r="F1010" s="28" t="str">
+        <x:v>Generación fotorrealista actual, sin cambios.</x:v>
+      </x:c>
+      <x:c r="G1010" s="28" t="str">
+        <x:v>Aktuelle fotorealistische Generierung, unverändert.</x:v>
+      </x:c>
+      <x:c r="H1010" s="28" t="str">
+        <x:v>Added by v40.0.9 visual style</x:v>
+      </x:c>
+      <x:c r="I1010" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1010" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011">
+      <x:c r="A1011" s="28" t="str">
+        <x:v>char.visual_style.anime_title</x:v>
+      </x:c>
+      <x:c r="B1011" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1011" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1011" s="28" t="str">
+        <x:v>Créateur anime</x:v>
+      </x:c>
+      <x:c r="E1011" s="28" t="str">
+        <x:v>Anime creator</x:v>
+      </x:c>
+      <x:c r="F1011" s="28" t="str">
+        <x:v>Creador anime</x:v>
+      </x:c>
+      <x:c r="G1011" s="28" t="str">
+        <x:v>Anime-Ersteller</x:v>
+      </x:c>
+      <x:c r="H1011" s="28" t="str">
+        <x:v>Added by v40.0.9 visual style</x:v>
+      </x:c>
+      <x:c r="I1011" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1011" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012">
+      <x:c r="A1012" s="28" t="str">
+        <x:v>char.visual_style.anime_desc</x:v>
+      </x:c>
+      <x:c r="B1012" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1012" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1012" s="28" t="str">
+        <x:v>Prompts anime et bibliothèque d’aperçus anime séparée.</x:v>
+      </x:c>
+      <x:c r="E1012" s="28" t="str">
+        <x:v>Anime prompts and a separate anime preview library.</x:v>
+      </x:c>
+      <x:c r="F1012" s="28" t="str">
+        <x:v>Prompts anime y una biblioteca de vistas previas anime independiente.</x:v>
+      </x:c>
+      <x:c r="G1012" s="28" t="str">
+        <x:v>Anime-Prompts und eine separate Anime-Vorschaubibliothek.</x:v>
+      </x:c>
+      <x:c r="H1012" s="28" t="str">
+        <x:v>Added by v40.0.9 visual style</x:v>
+      </x:c>
+      <x:c r="I1012" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1012" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013">
+      <x:c r="A1013" s="28" t="str">
+        <x:v>char.visual_style.cartoon_title</x:v>
+      </x:c>
+      <x:c r="B1013" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1013" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1013" s="28" t="str">
+        <x:v>Créateur cartoon</x:v>
+      </x:c>
+      <x:c r="E1013" s="28" t="str">
+        <x:v>Cartoon creator</x:v>
+      </x:c>
+      <x:c r="F1013" s="28" t="str">
+        <x:v>Creador cartoon</x:v>
+      </x:c>
+      <x:c r="G1013" s="28" t="str">
+        <x:v>Cartoon-Ersteller</x:v>
+      </x:c>
+      <x:c r="H1013" s="28" t="str">
+        <x:v>Added by v40.0.9 visual style</x:v>
+      </x:c>
+      <x:c r="I1013" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1013" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014">
+      <x:c r="A1014" s="28" t="str">
+        <x:v>char.visual_style.cartoon_desc</x:v>
+      </x:c>
+      <x:c r="B1014" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1014" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1014" s="28" t="str">
+        <x:v>Prompts cartoon et bibliothèque d’aperçus cartoon séparée.</x:v>
+      </x:c>
+      <x:c r="E1014" s="28" t="str">
+        <x:v>Cartoon prompts and a separate cartoon preview library.</x:v>
+      </x:c>
+      <x:c r="F1014" s="28" t="str">
+        <x:v>Prompts cartoon y una biblioteca de vistas previas cartoon independiente.</x:v>
+      </x:c>
+      <x:c r="G1014" s="28" t="str">
+        <x:v>Cartoon-Prompts und eine separate Cartoon-Vorschaubibliothek.</x:v>
+      </x:c>
+      <x:c r="H1014" s="28" t="str">
+        <x:v>Added by v40.0.9 visual style</x:v>
+      </x:c>
+      <x:c r="I1014" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1014" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015">
+      <x:c r="A1015" s="28" t="str">
+        <x:v>char.visual_style.switched</x:v>
+      </x:c>
+      <x:c r="B1015" s="28" t="str">
+        <x:v>char</x:v>
+      </x:c>
+      <x:c r="C1015" s="28" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1015" s="28" t="str">
+        <x:v>Section active : {style}</x:v>
+      </x:c>
+      <x:c r="E1015" s="28" t="str">
+        <x:v>Active section: {style}</x:v>
+      </x:c>
+      <x:c r="F1015" s="28" t="str">
+        <x:v>Sección activa: {style}</x:v>
+      </x:c>
+      <x:c r="G1015" s="28" t="str">
+        <x:v>Aktiver Bereich: {style}</x:v>
+      </x:c>
+      <x:c r="H1015" s="28" t="str">
+        <x:v>Added by v40.0.9 isolated creator state</x:v>
+      </x:c>
+      <x:c r="I1015" s="28" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1015" s="28" t="str">
         <x:v>ok</x:v>
       </x:c>
     </x:row>
@@ -31993,7 +32281,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>40.0.7</x:v>
+        <x:v>40.0.9</x:v>
       </x:c>
     </x:row>
     <x:row r="6">

--- a/resources/i18n/translations_master.xlsx
+++ b/resources/i18n/translations_master.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="R1f966a4abed0466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="R4994c2dd9be74e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="Rc372d3b3e4ba421a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="Rda33240f16e94c9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" r:id="Rd1aa8191aa4c4ab3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="2" r:id="Ra73f54a19ce94835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" r:id="R884fac50eb7f4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" r:id="R81dc7d16a4f14097"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -802,19 +802,23 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D14" s="3" t="str">
-        <x:v>100 % local — LLM + ComfyUI</x:v>
+        <x:v>Local d’abord — moteurs locaux ou services personnels</x:v>
       </x:c>
       <x:c r="E14" s="3" t="str">
-        <x:v>100% local — LLM + ComfyUI</x:v>
+        <x:v>Local-first — local or user-owned AI engines</x:v>
       </x:c>
       <x:c r="F14" s="3" t="str">
-        <x:v>100% local — LLM + ComfyUI</x:v>
+        <x:v>Local primero — motores locales o servicios propios</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>100% lokal — LLM + ComfyUI</x:v>
-      </x:c>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
+        <x:v>Local-first — lokale oder eigene KI-Dienste</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="str">
+        <x:v>Updated by v40.1.0 remote providers</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J14" s="3" t="str">
         <x:v>ok</x:v>
       </x:c>
@@ -9576,23 +9580,25 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D309" s="4" t="str">
-        <x:v>Un seul programme charge ton LLM et ton modèle image. Tout reste sur ta machine.</x:v>
+        <x:v>Choisis des moteurs locaux ou connecte tes propres services. Les données du compagnon restent locales ; seuls les appels envoyés à un fournisseur distant le quittent.</x:v>
       </x:c>
       <x:c r="E309" s="4" t="str">
-        <x:v>One program loads your LLM and image model. Everything stays on your machine.</x:v>
+        <x:v>Choose local engines or connect services you own. Companion data stays local; remote providers receive only requests sent to them.</x:v>
       </x:c>
       <x:c r="F309" s="4" t="str">
-        <x:v>One program loads your LLM and image model. Everything stays on your machine.</x:v>
+        <x:v>Elige motores locales o conecta tus propios servicios. Los datos del compañero permanecen locales; solo salen las solicitudes enviadas a un proveedor remoto.</x:v>
       </x:c>
       <x:c r="G309" s="4" t="str">
-        <x:v>One program loads your LLM and image model. Everything stays on your machine.</x:v>
+        <x:v>Wähle lokale Engines oder verbinde eigene Dienste. Begleiterdaten bleiben lokal; nur ausdrücklich gesendete Remote-Anfragen verlassen den PC.</x:v>
       </x:c>
       <x:c r="H309" s="4" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I309" s="4"/>
+        <x:v>Updated by v40.1.0 remote providers</x:v>
+      </x:c>
+      <x:c r="I309" s="4" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J309" s="4" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -10372,16 +10378,16 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D336" s="4" t="str">
-        <x:v>Cette valeur doit rester égale ou inférieure au contexte réellement configuré pour le modèle dans LM Studio.</x:v>
+        <x:v>Cette valeur doit rester égale ou inférieure au contexte réellement configuré pour le modèle chez le fournisseur sélectionné.</x:v>
       </x:c>
       <x:c r="E336" s="4" t="str">
-        <x:v>This value must be equal to or less than the context actually configured for the model in LM Studio.</x:v>
+        <x:v>This value must be equal to or lower than the context actually configured for the model on the selected provider.</x:v>
       </x:c>
       <x:c r="F336" s="4" t="str">
-        <x:v>This value must be equal to or less than the context actually configured for the model in LM Studio.</x:v>
+        <x:v>Este valor debe ser igual o inferior al contexto configurado realmente para el modelo en el proveedor seleccionado.</x:v>
       </x:c>
       <x:c r="G336" s="4" t="str">
-        <x:v>This value must be equal to or less than the context actually configured for the model in LM Studio.</x:v>
+        <x:v>Dieser Wert muss kleiner oder gleich dem tatsächlich beim ausgewählten Anbieter konfigurierten Modellkontext sein.</x:v>
       </x:c>
       <x:c r="H336" s="4" t="str">
         <x:v>English fallback pending localized review</x:v>
@@ -10489,26 +10495,28 @@
         <x:v>settings</x:v>
       </x:c>
       <x:c r="C340" s="4" t="str">
-        <x:v>text</x:v>
+        <x:v>html</x:v>
       </x:c>
       <x:c r="D340" s="4" t="str">
-        <x:v>Astuce qualité : un modèle de &lt;b&gt;roleplay&lt;/b&gt; (souvent non censuré) est mauvais pour produire du JSON propre et des prompts d'image structurés.</x:v>
+        <x:v>Astuce qualité : un modèle de &lt;b&gt;roleplay&lt;/b&gt; (souvent non censuré) est mauvais pour produire du JSON propre et des prompts d’image structurés.</x:v>
       </x:c>
       <x:c r="E340" s="4" t="str">
         <x:v>Quality tip: a &lt;b&gt;roleplay&lt;/b&gt; model (often uncensored) is poor at producing clean JSON and structured image prompts.</x:v>
       </x:c>
       <x:c r="F340" s="4" t="str">
-        <x:v>Quality tip: a &lt;b&gt;roleplay&lt;/b&gt; model (often uncensored) is poor at producing clean JSON and structured image prompts.</x:v>
+        <x:v>Consejo de calidad: un modelo de &lt;b&gt;roleplay&lt;/b&gt; (a menudo sin censura) suele producir peor JSON limpio y prompts de imagen estructurados.</x:v>
       </x:c>
       <x:c r="G340" s="4" t="str">
-        <x:v>Quality tip: a &lt;b&gt;roleplay&lt;/b&gt; model (often uncensored) is poor at producing clean JSON and structured image prompts.</x:v>
+        <x:v>Qualitätstipp: Ein &lt;b&gt;Roleplay&lt;/b&gt;-Modell (oft unzensiert) eignet sich meist schlecht für sauberes JSON und strukturierte Bild-Prompts.</x:v>
       </x:c>
       <x:c r="H340" s="4" t="str">
-        <x:v>English fallback pending localized review</x:v>
-      </x:c>
-      <x:c r="I340" s="4"/>
+        <x:v>Corrected ES/DE and retained by v40.1.0</x:v>
+      </x:c>
+      <x:c r="I340" s="4" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
       <x:c r="J340" s="4" t="str">
-        <x:v>fallback_en</x:v>
+        <x:v>ok</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -11044,19 +11052,19 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D358" s="4" t="str">
-        <x:v>Connexion ComfyUI tiers</x:v>
+        <x:v>Fournisseur de génération d’images</x:v>
       </x:c>
       <x:c r="E358" s="4" t="str">
-        <x:v>External ComfyUI connection</x:v>
+        <x:v>Image generation provider</x:v>
       </x:c>
       <x:c r="F358" s="4" t="str">
-        <x:v>Conexión con ComfyUI externo</x:v>
+        <x:v>Proveedor de generación de imágenes</x:v>
       </x:c>
       <x:c r="G358" s="4" t="str">
-        <x:v>Verbindung zu externem ComfyUI</x:v>
+        <x:v>Anbieter für Bildgenerierung</x:v>
       </x:c>
       <x:c r="H358" s="4" t="str">
-        <x:v>v40.0.7 external ComfyUI only</x:v>
+        <x:v>Updated by v40.1.0 remote image providers</x:v>
       </x:c>
       <x:c r="I358" s="4" t="str">
         <x:v>resources/i18n/locales/*.json</x:v>
@@ -11076,19 +11084,19 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D359" s="4" t="str">
-        <x:v>AmiorAI se connecte uniquement à une installation ComfyUI tierce déjà démarrée. Il n’installe, ne lance, ne redémarre et n’arrête jamais ComfyUI. Les modèles et workflows se choisissent dans &lt;strong&gt;Studio Image&lt;/strong&gt;.</x:v>
+        <x:v>Choisis un moteur d’image local ou distant qui t’appartient. AmiorAI ne vend pas de calcul et ne gère pas la facturation du fournisseur.</x:v>
       </x:c>
       <x:c r="E359" s="4" t="str">
-        <x:v>AmiorAI only connects to an already running third-party ComfyUI installation. It never installs, launches, restarts or stops ComfyUI. Image models and workflows are selected in &lt;strong&gt;Image Studio&lt;/strong&gt;.</x:v>
+        <x:v>Choose a local or user-owned remote image engine. AmiorAI does not sell compute and does not manage provider billing.</x:v>
       </x:c>
       <x:c r="F359" s="4" t="str">
-        <x:v>AmiorAI solo se conecta a una instalación de ComfyUI de terceros que ya esté en ejecución. Nunca instala, inicia, reinicia ni detiene ComfyUI. Los modelos y flujos de trabajo se eligen en &lt;strong&gt;Estudio de imágenes&lt;/strong&gt;.</x:v>
+        <x:v>Elige un motor de imágenes local o remoto de tu propiedad. AmiorAI no vende cómputo ni gestiona la facturación.</x:v>
       </x:c>
       <x:c r="G359" s="4" t="str">
-        <x:v>AmiorAI verbindet sich nur mit einer bereits laufenden ComfyUI-Installation eines Drittanbieters. ComfyUI wird niemals von AmiorAI installiert, gestartet, neu gestartet oder beendet. Modelle und Workflows werden in &lt;strong&gt;Image Studio&lt;/strong&gt; ausgewählt.</x:v>
+        <x:v>Wähle eine lokale oder eigene entfernte Bild-Engine. AmiorAI verkauft keine Rechenleistung und verwaltet keine Anbieterabrechnung.</x:v>
       </x:c>
       <x:c r="H359" s="4" t="str">
-        <x:v>v40.0.7 external ComfyUI only</x:v>
+        <x:v>Updated by v40.1.0 remote image providers</x:v>
       </x:c>
       <x:c r="I359" s="4" t="str">
         <x:v>resources/i18n/locales/*.json</x:v>
@@ -28484,19 +28492,19 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="D908" s="28" t="str">
-        <x:v>Le modèle utilitaire utilise le même serveur LM Studio et la même clé API.</x:v>
+        <x:v>Le modèle utilitaire utilise le même fournisseur et les mêmes identifiants que le modèle conversationnel.</x:v>
       </x:c>
       <x:c r="E908" s="28" t="str">
-        <x:v>The utility model uses the same LM Studio server and API key.</x:v>
+        <x:v>The utility model uses the same selected provider and credentials as the conversation model.</x:v>
       </x:c>
       <x:c r="F908" s="28" t="str">
-        <x:v>El modelo utilitario usa el mismo servidor LM Studio y la misma clave API.</x:v>
+        <x:v>El modelo utilitario usa el mismo proveedor y las mismas credenciales que el modelo de conversación.</x:v>
       </x:c>
       <x:c r="G908" s="28" t="str">
-        <x:v>Das Hilfsmodell verwendet denselben LM-Studio-Server und API-Schlüssel.</x:v>
+        <x:v>Das Hilfsmodell verwendet denselben ausgewählten Anbieter und dieselben Zugangsdaten wie das Konversationsmodell.</x:v>
       </x:c>
       <x:c r="H908" s="28" t="str">
-        <x:v>Added by v39.1.0 non-destructive merge</x:v>
+        <x:v>Updated by v40.1.0 provider abstraction</x:v>
       </x:c>
       <x:c r="I908" s="28" t="str">
         <x:v>resources/i18n/locales/*.json</x:v>
@@ -31926,6 +31934,1990 @@
         <x:v>resources/i18n/locales/*.json</x:v>
       </x:c>
       <x:c r="J1015" s="28" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016">
+      <x:c r="A1016" t="str">
+        <x:v>settings.providers_privacy_hint</x:v>
+      </x:c>
+      <x:c r="B1016" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1016" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1016" t="str">
+        <x:v>Le mode local garde les prompts sur ce PC. Les modes distants envoient uniquement les données nécessaires à la tâche au fournisseur configuré par l’utilisateur.</x:v>
+      </x:c>
+      <x:c r="E1016" t="str">
+        <x:v>Local mode keeps prompts on this PC. Remote modes send only the data required for the selected task to the provider configured by the user.</x:v>
+      </x:c>
+      <x:c r="F1016" t="str">
+        <x:v>El modo local conserva los prompts en este PC. Los modos remotos envían únicamente los datos necesarios al proveedor configurado por el usuario.</x:v>
+      </x:c>
+      <x:c r="G1016" t="str">
+        <x:v>Im lokalen Modus bleiben Prompts auf diesem PC. Remote-Modi senden nur die für die Aufgabe nötigen Daten an den vom Benutzer konfigurierten Anbieter.</x:v>
+      </x:c>
+      <x:c r="H1016" t="str">
+        <x:v>Added by v40.1.0 remote providers</x:v>
+      </x:c>
+      <x:c r="I1016" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1016" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017">
+      <x:c r="A1017" t="str">
+        <x:v>settings.llm_provider_label</x:v>
+      </x:c>
+      <x:c r="B1017" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1017" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1017" t="str">
+        <x:v>Fournisseur de conversation</x:v>
+      </x:c>
+      <x:c r="E1017" t="str">
+        <x:v>Conversation provider</x:v>
+      </x:c>
+      <x:c r="F1017" t="str">
+        <x:v>Proveedor de conversación</x:v>
+      </x:c>
+      <x:c r="G1017" t="str">
+        <x:v>Konversationsanbieter</x:v>
+      </x:c>
+      <x:c r="H1017" t="str">
+        <x:v>Added by v40.1.0 remote LLM providers</x:v>
+      </x:c>
+      <x:c r="I1017" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1017" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018">
+      <x:c r="A1018" t="str">
+        <x:v>settings.image_provider_hint</x:v>
+      </x:c>
+      <x:c r="B1018" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1018" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1018" t="str">
+        <x:v>Choisis ComfyUI local, un serveur ComfyUI distant, Runpod Serverless ou ton propre Pod Runpod.</x:v>
+      </x:c>
+      <x:c r="E1018" t="str">
+        <x:v>Choose local ComfyUI, a remote ComfyUI-compatible server, Runpod Serverless, or a user-owned Runpod Pod.</x:v>
+      </x:c>
+      <x:c r="F1018" t="str">
+        <x:v>Elige ComfyUI local, un servidor ComfyUI remoto, Runpod Serverless o tu propio Pod de Runpod.</x:v>
+      </x:c>
+      <x:c r="G1018" t="str">
+        <x:v>Wähle lokales ComfyUI, einen entfernten ComfyUI-Server, Runpod Serverless oder deinen eigenen Runpod-Pod.</x:v>
+      </x:c>
+      <x:c r="H1018" t="str">
+        <x:v>Added by v40.1.0 remote image providers</x:v>
+      </x:c>
+      <x:c r="I1018" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1018" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019">
+      <x:c r="A1019" t="str">
+        <x:v>settings.image_provider_label</x:v>
+      </x:c>
+      <x:c r="B1019" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1019" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1019" t="str">
+        <x:v>Fournisseur d’images</x:v>
+      </x:c>
+      <x:c r="E1019" t="str">
+        <x:v>Image provider</x:v>
+      </x:c>
+      <x:c r="F1019" t="str">
+        <x:v>Proveedor de imágenes</x:v>
+      </x:c>
+      <x:c r="G1019" t="str">
+        <x:v>Bildanbieter</x:v>
+      </x:c>
+      <x:c r="H1019" t="str">
+        <x:v>Added by v40.1.0 remote image providers</x:v>
+      </x:c>
+      <x:c r="I1019" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1019" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020">
+      <x:c r="A1020" t="str">
+        <x:v>settings.runpod_title</x:v>
+      </x:c>
+      <x:c r="B1020" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1020" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1020" t="str">
+        <x:v>Compte Runpod et arrêt automatique des Pods</x:v>
+      </x:c>
+      <x:c r="E1020" t="str">
+        <x:v>Runpod account and Pod policy</x:v>
+      </x:c>
+      <x:c r="F1020" t="str">
+        <x:v>Cuenta Runpod y política de Pods</x:v>
+      </x:c>
+      <x:c r="G1020" t="str">
+        <x:v>Runpod-Konto und Pod-Richtlinie</x:v>
+      </x:c>
+      <x:c r="H1020" t="str">
+        <x:v>Added by v40.1.0 Runpod controls</x:v>
+      </x:c>
+      <x:c r="I1020" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1020" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021">
+      <x:c r="A1021" t="str">
+        <x:v>settings.runpod_hint</x:v>
+      </x:c>
+      <x:c r="B1021" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1021" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1021" t="str">
+        <x:v>AmiorAI ne vend ni calcul ni crédits. Cette clé pilote uniquement le compte Runpod qui t’appartient et qui te facture directement.</x:v>
+      </x:c>
+      <x:c r="E1021" t="str">
+        <x:v>AmiorAI never sells compute or credits. This key controls only the Runpod account owned and billed directly to you.</x:v>
+      </x:c>
+      <x:c r="F1021" t="str">
+        <x:v>AmiorAI no vende cómputo ni créditos. Esta clave controla únicamente tu propia cuenta de Runpod, facturada directamente por Runpod.</x:v>
+      </x:c>
+      <x:c r="G1021" t="str">
+        <x:v>AmiorAI verkauft weder Rechenleistung noch Guthaben. Dieser Schlüssel steuert ausschließlich dein eigenes, direkt von Runpod abgerechnetes Konto.</x:v>
+      </x:c>
+      <x:c r="H1021" t="str">
+        <x:v>Added by v40.1.0 Runpod controls</x:v>
+      </x:c>
+      <x:c r="I1021" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1021" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022">
+      <x:c r="A1022" t="str">
+        <x:v>settings.llm_provider_lmstudio_opt</x:v>
+      </x:c>
+      <x:c r="B1022" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1022" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1022" t="str">
+        <x:v>LM Studio — local</x:v>
+      </x:c>
+      <x:c r="E1022" t="str">
+        <x:v>LM Studio — local</x:v>
+      </x:c>
+      <x:c r="F1022" t="str">
+        <x:v>LM Studio — local</x:v>
+      </x:c>
+      <x:c r="G1022" t="str">
+        <x:v>LM Studio — lokal</x:v>
+      </x:c>
+      <x:c r="H1022" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1022" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1022" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023">
+      <x:c r="A1023" t="str">
+        <x:v>settings.llm_provider_openai_opt</x:v>
+      </x:c>
+      <x:c r="B1023" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1023" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1023" t="str">
+        <x:v>API compatible OpenAI — serveur de l’utilisateur</x:v>
+      </x:c>
+      <x:c r="E1023" t="str">
+        <x:v>OpenAI-compatible API — user-owned server</x:v>
+      </x:c>
+      <x:c r="F1023" t="str">
+        <x:v>API compatible con OpenAI — servidor del usuario</x:v>
+      </x:c>
+      <x:c r="G1023" t="str">
+        <x:v>OpenAI-kompatible API — eigener Server</x:v>
+      </x:c>
+      <x:c r="H1023" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1023" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1023" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024">
+      <x:c r="A1024" t="str">
+        <x:v>settings.llm_provider_serverless_opt</x:v>
+      </x:c>
+      <x:c r="B1024" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1024" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1024" t="str">
+        <x:v>Runpod Serverless — vLLM</x:v>
+      </x:c>
+      <x:c r="E1024" t="str">
+        <x:v>Runpod Serverless — vLLM</x:v>
+      </x:c>
+      <x:c r="F1024" t="str">
+        <x:v>Runpod Serverless — vLLM</x:v>
+      </x:c>
+      <x:c r="G1024" t="str">
+        <x:v>Runpod Serverless — vLLM</x:v>
+      </x:c>
+      <x:c r="H1024" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1024" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1024" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025">
+      <x:c r="A1025" t="str">
+        <x:v>settings.llm_provider_pod_opt</x:v>
+      </x:c>
+      <x:c r="B1025" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1025" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1025" t="str">
+        <x:v>Runpod Pod — vLLM</x:v>
+      </x:c>
+      <x:c r="E1025" t="str">
+        <x:v>Runpod Pod — vLLM</x:v>
+      </x:c>
+      <x:c r="F1025" t="str">
+        <x:v>Runpod Pod — vLLM</x:v>
+      </x:c>
+      <x:c r="G1025" t="str">
+        <x:v>Runpod Pod — vLLM</x:v>
+      </x:c>
+      <x:c r="H1025" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1025" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1025" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026">
+      <x:c r="A1026" t="str">
+        <x:v>settings.llm_local_url_label</x:v>
+      </x:c>
+      <x:c r="B1026" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1026" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1026" t="str">
+        <x:v>Adresse du serveur LM Studio</x:v>
+      </x:c>
+      <x:c r="E1026" t="str">
+        <x:v>LM Studio server URL</x:v>
+      </x:c>
+      <x:c r="F1026" t="str">
+        <x:v>URL del servidor LM Studio</x:v>
+      </x:c>
+      <x:c r="G1026" t="str">
+        <x:v>Adresse des LM-Studio-Servers</x:v>
+      </x:c>
+      <x:c r="H1026" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1026" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1026" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027">
+      <x:c r="A1027" t="str">
+        <x:v>settings.llm_conversation_model_label</x:v>
+      </x:c>
+      <x:c r="B1027" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1027" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1027" t="str">
+        <x:v>Modèle de conversation</x:v>
+      </x:c>
+      <x:c r="E1027" t="str">
+        <x:v>Conversation model</x:v>
+      </x:c>
+      <x:c r="F1027" t="str">
+        <x:v>Modelo de conversación</x:v>
+      </x:c>
+      <x:c r="G1027" t="str">
+        <x:v>Konversationsmodell</x:v>
+      </x:c>
+      <x:c r="H1027" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1027" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1027" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028">
+      <x:c r="A1028" t="str">
+        <x:v>settings.llm_refresh_models_btn</x:v>
+      </x:c>
+      <x:c r="B1028" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1028" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1028" t="str">
+        <x:v>Actualiser la liste des modèles</x:v>
+      </x:c>
+      <x:c r="E1028" t="str">
+        <x:v>Refresh model list</x:v>
+      </x:c>
+      <x:c r="F1028" t="str">
+        <x:v>Actualizar lista de modelos</x:v>
+      </x:c>
+      <x:c r="G1028" t="str">
+        <x:v>Modellliste aktualisieren</x:v>
+      </x:c>
+      <x:c r="H1028" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1028" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1028" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029">
+      <x:c r="A1029" t="str">
+        <x:v>settings.llm_local_start_hint</x:v>
+      </x:c>
+      <x:c r="B1029" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1029" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1029" t="str">
+        <x:v>Lance LM Studio, charge un modèle, démarre son serveur local, puis clique sur « Tester » ci-dessus.</x:v>
+      </x:c>
+      <x:c r="E1029" t="str">
+        <x:v>Start LM Studio, load a model, start its local server, then click Test above.</x:v>
+      </x:c>
+      <x:c r="F1029" t="str">
+        <x:v>Inicia LM Studio, carga un modelo, inicia su servidor local y pulsa Probar arriba.</x:v>
+      </x:c>
+      <x:c r="G1029" t="str">
+        <x:v>Starte LM Studio, lade ein Modell, starte den lokalen Server und klicke oben auf Testen.</x:v>
+      </x:c>
+      <x:c r="H1029" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1029" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1029" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030">
+      <x:c r="A1030" t="str">
+        <x:v>settings.llm_remote_url_label</x:v>
+      </x:c>
+      <x:c r="B1030" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1030" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1030" t="str">
+        <x:v>Adresse de l’API compatible OpenAI</x:v>
+      </x:c>
+      <x:c r="E1030" t="str">
+        <x:v>OpenAI-compatible API URL</x:v>
+      </x:c>
+      <x:c r="F1030" t="str">
+        <x:v>URL de la API compatible con OpenAI</x:v>
+      </x:c>
+      <x:c r="G1030" t="str">
+        <x:v>Adresse der OpenAI-kompatiblen API</x:v>
+      </x:c>
+      <x:c r="H1030" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1030" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1030" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031">
+      <x:c r="A1031" t="str">
+        <x:v>settings.llm_remote_model_label</x:v>
+      </x:c>
+      <x:c r="B1031" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1031" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1031" t="str">
+        <x:v>Identifiant du modèle de conversation</x:v>
+      </x:c>
+      <x:c r="E1031" t="str">
+        <x:v>Conversation model ID</x:v>
+      </x:c>
+      <x:c r="F1031" t="str">
+        <x:v>ID del modelo de conversación</x:v>
+      </x:c>
+      <x:c r="G1031" t="str">
+        <x:v>ID des Konversationsmodells</x:v>
+      </x:c>
+      <x:c r="H1031" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1031" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1031" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032">
+      <x:c r="A1032" t="str">
+        <x:v>settings.remote_api_key_label</x:v>
+      </x:c>
+      <x:c r="B1032" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1032" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1032" t="str">
+        <x:v>Clé API du service (optionnelle)</x:v>
+      </x:c>
+      <x:c r="E1032" t="str">
+        <x:v>Service API key (optional)</x:v>
+      </x:c>
+      <x:c r="F1032" t="str">
+        <x:v>Clave API del servicio (opcional)</x:v>
+      </x:c>
+      <x:c r="G1032" t="str">
+        <x:v>API-Schlüssel des Dienstes (optional)</x:v>
+      </x:c>
+      <x:c r="H1032" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1032" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1032" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033">
+      <x:c r="A1033" t="str">
+        <x:v>settings.secret_keep_placeholder</x:v>
+      </x:c>
+      <x:c r="B1033" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1033" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1033" t="str">
+        <x:v>Laisser vide pour conserver la clé enregistrée</x:v>
+      </x:c>
+      <x:c r="E1033" t="str">
+        <x:v>Leave blank to keep the saved key</x:v>
+      </x:c>
+      <x:c r="F1033" t="str">
+        <x:v>Déjalo vacío para conservar la clave guardada</x:v>
+      </x:c>
+      <x:c r="G1033" t="str">
+        <x:v>Leer lassen, um den gespeicherten Schlüssel zu behalten</x:v>
+      </x:c>
+      <x:c r="H1033" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1033" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1033" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034">
+      <x:c r="A1034" t="str">
+        <x:v>settings.serverless_endpoint_label</x:v>
+      </x:c>
+      <x:c r="B1034" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1034" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1034" t="str">
+        <x:v>Identifiant de l’endpoint Runpod Serverless</x:v>
+      </x:c>
+      <x:c r="E1034" t="str">
+        <x:v>Runpod Serverless endpoint ID</x:v>
+      </x:c>
+      <x:c r="F1034" t="str">
+        <x:v>ID del endpoint Runpod Serverless</x:v>
+      </x:c>
+      <x:c r="G1034" t="str">
+        <x:v>ID des Runpod-Serverless-Endpunkts</x:v>
+      </x:c>
+      <x:c r="H1034" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1034" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1034" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035">
+      <x:c r="A1035" t="str">
+        <x:v>settings.llm_serverless_model_label</x:v>
+      </x:c>
+      <x:c r="B1035" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1035" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1035" t="str">
+        <x:v>Identifiant du modèle exposé par vLLM</x:v>
+      </x:c>
+      <x:c r="E1035" t="str">
+        <x:v>Model ID exposed by vLLM</x:v>
+      </x:c>
+      <x:c r="F1035" t="str">
+        <x:v>ID del modelo expuesto por vLLM</x:v>
+      </x:c>
+      <x:c r="G1035" t="str">
+        <x:v>Von vLLM bereitgestellte Modell-ID</x:v>
+      </x:c>
+      <x:c r="H1035" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1035" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1035" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036">
+      <x:c r="A1036" t="str">
+        <x:v>settings.llm_serverless_hint</x:v>
+      </x:c>
+      <x:c r="B1036" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1036" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1036" t="str">
+        <x:v>L’endpoint démarre un worker Flex à la demande. Réglage conseillé : 0 worker minimum et délai d’inactivité de 900 secondes.</x:v>
+      </x:c>
+      <x:c r="E1036" t="str">
+        <x:v>The endpoint starts a Flex worker on demand. Recommended setting: 0 minimum workers and a 900-second idle timeout.</x:v>
+      </x:c>
+      <x:c r="F1036" t="str">
+        <x:v>El endpoint inicia un worker Flex bajo demanda. Ajuste recomendado: 0 workers mínimos y 900 segundos de inactividad.</x:v>
+      </x:c>
+      <x:c r="G1036" t="str">
+        <x:v>Der Endpunkt startet bei Bedarf einen Flex-Worker. Empfohlen: 0 minimale Worker und 900 Sekunden Leerlaufzeit.</x:v>
+      </x:c>
+      <x:c r="H1036" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1036" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1036" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037">
+      <x:c r="A1037" t="str">
+        <x:v>settings.runpod_pod_id_label</x:v>
+      </x:c>
+      <x:c r="B1037" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1037" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1037" t="str">
+        <x:v>Identifiant du Pod Runpod</x:v>
+      </x:c>
+      <x:c r="E1037" t="str">
+        <x:v>Runpod Pod ID</x:v>
+      </x:c>
+      <x:c r="F1037" t="str">
+        <x:v>ID del Pod Runpod</x:v>
+      </x:c>
+      <x:c r="G1037" t="str">
+        <x:v>Runpod-Pod-ID</x:v>
+      </x:c>
+      <x:c r="H1037" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1037" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1037" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038">
+      <x:c r="A1038" t="str">
+        <x:v>settings.llm_pod_url_label</x:v>
+      </x:c>
+      <x:c r="B1038" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1038" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1038" t="str">
+        <x:v>Adresse API compatible OpenAI du Pod</x:v>
+      </x:c>
+      <x:c r="E1038" t="str">
+        <x:v>Pod OpenAI-compatible API URL</x:v>
+      </x:c>
+      <x:c r="F1038" t="str">
+        <x:v>URL de API compatible con OpenAI del Pod</x:v>
+      </x:c>
+      <x:c r="G1038" t="str">
+        <x:v>OpenAI-kompatible API-Adresse des Pods</x:v>
+      </x:c>
+      <x:c r="H1038" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1038" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1038" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039">
+      <x:c r="A1039" t="str">
+        <x:v>settings.pod_start_timeout_label</x:v>
+      </x:c>
+      <x:c r="B1039" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1039" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1039" t="str">
+        <x:v>Attente maximale du démarrage du Pod (secondes)</x:v>
+      </x:c>
+      <x:c r="E1039" t="str">
+        <x:v>Maximum Pod startup wait (seconds)</x:v>
+      </x:c>
+      <x:c r="F1039" t="str">
+        <x:v>Espera máxima de inicio del Pod (segundos)</x:v>
+      </x:c>
+      <x:c r="G1039" t="str">
+        <x:v>Maximale Wartezeit beim Pod-Start (Sekunden)</x:v>
+      </x:c>
+      <x:c r="H1039" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1039" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1039" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040">
+      <x:c r="A1040" t="str">
+        <x:v>settings.llm_pod_start_btn</x:v>
+      </x:c>
+      <x:c r="B1040" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1040" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1040" t="str">
+        <x:v>Démarrer le Pod LLM</x:v>
+      </x:c>
+      <x:c r="E1040" t="str">
+        <x:v>Start LLM Pod</x:v>
+      </x:c>
+      <x:c r="F1040" t="str">
+        <x:v>Iniciar Pod LLM</x:v>
+      </x:c>
+      <x:c r="G1040" t="str">
+        <x:v>LLM-Pod starten</x:v>
+      </x:c>
+      <x:c r="H1040" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1040" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1040" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041">
+      <x:c r="A1041" t="str">
+        <x:v>settings.llm_pod_stop_btn</x:v>
+      </x:c>
+      <x:c r="B1041" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1041" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1041" t="str">
+        <x:v>Arrêter le Pod LLM</x:v>
+      </x:c>
+      <x:c r="E1041" t="str">
+        <x:v>Stop LLM Pod</x:v>
+      </x:c>
+      <x:c r="F1041" t="str">
+        <x:v>Detener Pod LLM</x:v>
+      </x:c>
+      <x:c r="G1041" t="str">
+        <x:v>LLM-Pod stoppen</x:v>
+      </x:c>
+      <x:c r="H1041" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1041" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1041" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042">
+      <x:c r="A1042" t="str">
+        <x:v>settings.model_auto_placeholder</x:v>
+      </x:c>
+      <x:c r="B1042" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1042" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1042" t="str">
+        <x:v>— automatique / seul modèle chargé —</x:v>
+      </x:c>
+      <x:c r="E1042" t="str">
+        <x:v>— automatic / only loaded model —</x:v>
+      </x:c>
+      <x:c r="F1042" t="str">
+        <x:v>— automático / único modelo cargado —</x:v>
+      </x:c>
+      <x:c r="G1042" t="str">
+        <x:v>— automatisch / einzig geladenes Modell —</x:v>
+      </x:c>
+      <x:c r="H1042" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1042" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1042" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043">
+      <x:c r="A1043" t="str">
+        <x:v>settings.model_detect_placeholder</x:v>
+      </x:c>
+      <x:c r="B1043" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1043" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1043" t="str">
+        <x:v>— détecter / choisir un modèle —</x:v>
+      </x:c>
+      <x:c r="E1043" t="str">
+        <x:v>— detect / select model —</x:v>
+      </x:c>
+      <x:c r="F1043" t="str">
+        <x:v>— detectar / elegir modelo —</x:v>
+      </x:c>
+      <x:c r="G1043" t="str">
+        <x:v>— Modell erkennen / auswählen —</x:v>
+      </x:c>
+      <x:c r="H1043" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1043" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1043" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1044">
+      <x:c r="A1044" t="str">
+        <x:v>settings.util_reuse_placeholder</x:v>
+      </x:c>
+      <x:c r="B1044" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1044" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1044" t="str">
+        <x:v>— réutiliser le modèle de conversation —</x:v>
+      </x:c>
+      <x:c r="E1044" t="str">
+        <x:v>— reuse conversation model —</x:v>
+      </x:c>
+      <x:c r="F1044" t="str">
+        <x:v>— reutilizar modelo de conversación —</x:v>
+      </x:c>
+      <x:c r="G1044" t="str">
+        <x:v>— Konversationsmodell wiederverwenden —</x:v>
+      </x:c>
+      <x:c r="H1044" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1044" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1044" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1045">
+      <x:c r="A1045" t="str">
+        <x:v>settings.image_provider_local_opt</x:v>
+      </x:c>
+      <x:c r="B1045" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1045" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1045" t="str">
+        <x:v>ComfyUI — local</x:v>
+      </x:c>
+      <x:c r="E1045" t="str">
+        <x:v>ComfyUI — local</x:v>
+      </x:c>
+      <x:c r="F1045" t="str">
+        <x:v>ComfyUI — local</x:v>
+      </x:c>
+      <x:c r="G1045" t="str">
+        <x:v>ComfyUI — lokal</x:v>
+      </x:c>
+      <x:c r="H1045" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1045" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1045" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1046">
+      <x:c r="A1046" t="str">
+        <x:v>settings.image_provider_remote_opt</x:v>
+      </x:c>
+      <x:c r="B1046" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1046" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1046" t="str">
+        <x:v>ComfyUI — API distante</x:v>
+      </x:c>
+      <x:c r="E1046" t="str">
+        <x:v>ComfyUI — remote API</x:v>
+      </x:c>
+      <x:c r="F1046" t="str">
+        <x:v>ComfyUI — API remota</x:v>
+      </x:c>
+      <x:c r="G1046" t="str">
+        <x:v>ComfyUI — Remote-API</x:v>
+      </x:c>
+      <x:c r="H1046" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1046" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1046" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1047">
+      <x:c r="A1047" t="str">
+        <x:v>settings.image_provider_serverless_opt</x:v>
+      </x:c>
+      <x:c r="B1047" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1047" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1047" t="str">
+        <x:v>Runpod Serverless — worker ComfyUI</x:v>
+      </x:c>
+      <x:c r="E1047" t="str">
+        <x:v>Runpod Serverless — ComfyUI worker</x:v>
+      </x:c>
+      <x:c r="F1047" t="str">
+        <x:v>Runpod Serverless — worker ComfyUI</x:v>
+      </x:c>
+      <x:c r="G1047" t="str">
+        <x:v>Runpod Serverless — ComfyUI-Worker</x:v>
+      </x:c>
+      <x:c r="H1047" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1047" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1047" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1048">
+      <x:c r="A1048" t="str">
+        <x:v>settings.image_provider_pod_opt</x:v>
+      </x:c>
+      <x:c r="B1048" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1048" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1048" t="str">
+        <x:v>Runpod Pod — ComfyUI</x:v>
+      </x:c>
+      <x:c r="E1048" t="str">
+        <x:v>Runpod Pod — ComfyUI</x:v>
+      </x:c>
+      <x:c r="F1048" t="str">
+        <x:v>Runpod Pod — ComfyUI</x:v>
+      </x:c>
+      <x:c r="G1048" t="str">
+        <x:v>Runpod Pod — ComfyUI</x:v>
+      </x:c>
+      <x:c r="H1048" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1048" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1048" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1049">
+      <x:c r="A1049" t="str">
+        <x:v>settings.image_remote_url_label</x:v>
+      </x:c>
+      <x:c r="B1049" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1049" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1049" t="str">
+        <x:v>Adresse de l’API ComfyUI distante</x:v>
+      </x:c>
+      <x:c r="E1049" t="str">
+        <x:v>Remote ComfyUI API URL</x:v>
+      </x:c>
+      <x:c r="F1049" t="str">
+        <x:v>URL de la API ComfyUI remota</x:v>
+      </x:c>
+      <x:c r="G1049" t="str">
+        <x:v>Adresse der entfernten ComfyUI-API</x:v>
+      </x:c>
+      <x:c r="H1049" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1049" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1049" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1050">
+      <x:c r="A1050" t="str">
+        <x:v>settings.image_serverless_hint</x:v>
+      </x:c>
+      <x:c r="B1050" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1050" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1050" t="str">
+        <x:v>Utilise le format AmiorAI pour ComfyUI : workflow et images de référence facultatives. L’endpoint démarre à la première génération.</x:v>
+      </x:c>
+      <x:c r="E1050" t="str">
+        <x:v>Uses the AmiorAI ComfyUI format: workflow plus optional reference images. The endpoint starts on the first generation.</x:v>
+      </x:c>
+      <x:c r="F1050" t="str">
+        <x:v>Usa el formato ComfyUI de AmiorAI: workflow e imágenes de referencia opcionales. El endpoint se inicia en la primera generación.</x:v>
+      </x:c>
+      <x:c r="G1050" t="str">
+        <x:v>Verwendet das AmiorAI-ComfyUI-Format: Workflow plus optionale Referenzbilder. Der Endpunkt startet bei der ersten Generierung.</x:v>
+      </x:c>
+      <x:c r="H1050" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1050" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1050" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1051">
+      <x:c r="A1051" t="str">
+        <x:v>settings.image_pod_url_label</x:v>
+      </x:c>
+      <x:c r="B1051" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1051" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1051" t="str">
+        <x:v>Adresse API ComfyUI du Pod</x:v>
+      </x:c>
+      <x:c r="E1051" t="str">
+        <x:v>Pod ComfyUI API URL</x:v>
+      </x:c>
+      <x:c r="F1051" t="str">
+        <x:v>URL de API ComfyUI del Pod</x:v>
+      </x:c>
+      <x:c r="G1051" t="str">
+        <x:v>ComfyUI-API-Adresse des Pods</x:v>
+      </x:c>
+      <x:c r="H1051" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1051" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1051" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1052">
+      <x:c r="A1052" t="str">
+        <x:v>settings.image_pod_start_btn</x:v>
+      </x:c>
+      <x:c r="B1052" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1052" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1052" t="str">
+        <x:v>Démarrer le Pod image</x:v>
+      </x:c>
+      <x:c r="E1052" t="str">
+        <x:v>Start Image Pod</x:v>
+      </x:c>
+      <x:c r="F1052" t="str">
+        <x:v>Iniciar Pod de imagen</x:v>
+      </x:c>
+      <x:c r="G1052" t="str">
+        <x:v>Bild-Pod starten</x:v>
+      </x:c>
+      <x:c r="H1052" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1052" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1052" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1053">
+      <x:c r="A1053" t="str">
+        <x:v>settings.image_pod_stop_btn</x:v>
+      </x:c>
+      <x:c r="B1053" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1053" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1053" t="str">
+        <x:v>Arrêter le Pod image</x:v>
+      </x:c>
+      <x:c r="E1053" t="str">
+        <x:v>Stop Image Pod</x:v>
+      </x:c>
+      <x:c r="F1053" t="str">
+        <x:v>Detener Pod de imagen</x:v>
+      </x:c>
+      <x:c r="G1053" t="str">
+        <x:v>Bild-Pod stoppen</x:v>
+      </x:c>
+      <x:c r="H1053" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1053" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1053" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1054">
+      <x:c r="A1054" t="str">
+        <x:v>settings.image_resolution_hint</x:v>
+      </x:c>
+      <x:c r="B1054" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1054" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1054" t="str">
+        <x:v>S’applique à toutes les générations sauf aux aperçus (512×512 fixe). Duo, Trio et Groupe utilisent la résolution de leur propre workflow.</x:v>
+      </x:c>
+      <x:c r="E1054" t="str">
+        <x:v>Applies to all generations except previews (fixed 512×512). Duo, Trio, and Group use their own workflow resolution.</x:v>
+      </x:c>
+      <x:c r="F1054" t="str">
+        <x:v>Se aplica a todas las generaciones excepto las vistas previas (512×512 fijo). Dúo, Trío y Grupo usan la resolución de su propio workflow.</x:v>
+      </x:c>
+      <x:c r="G1054" t="str">
+        <x:v>Gilt für alle Generierungen außer Vorschauen (fest 512×512). Duo, Trio und Gruppe verwenden die Auflösung ihres eigenen Workflows.</x:v>
+      </x:c>
+      <x:c r="H1054" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1054" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1054" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1055">
+      <x:c r="A1055" t="str">
+        <x:v>settings.runpod_api_key_label</x:v>
+      </x:c>
+      <x:c r="B1055" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1055" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1055" t="str">
+        <x:v>Clé API Runpod</x:v>
+      </x:c>
+      <x:c r="E1055" t="str">
+        <x:v>Runpod API key</x:v>
+      </x:c>
+      <x:c r="F1055" t="str">
+        <x:v>Clave API de Runpod</x:v>
+      </x:c>
+      <x:c r="G1055" t="str">
+        <x:v>Runpod-API-Schlüssel</x:v>
+      </x:c>
+      <x:c r="H1055" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1055" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1055" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1056">
+      <x:c r="A1056" t="str">
+        <x:v>settings.runpod_auto_stop_label</x:v>
+      </x:c>
+      <x:c r="B1056" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1056" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1056" t="str">
+        <x:v>Arrêter automatiquement un Pod après une période d’inactivité</x:v>
+      </x:c>
+      <x:c r="E1056" t="str">
+        <x:v>Automatically stop a Pod after inactivity</x:v>
+      </x:c>
+      <x:c r="F1056" t="str">
+        <x:v>Detener automáticamente un Pod tras un periodo de inactividad</x:v>
+      </x:c>
+      <x:c r="G1056" t="str">
+        <x:v>Pod nach Inaktivität automatisch stoppen</x:v>
+      </x:c>
+      <x:c r="H1056" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1056" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1056" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1057">
+      <x:c r="A1057" t="str">
+        <x:v>settings.runpod_idle_label</x:v>
+      </x:c>
+      <x:c r="B1057" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1057" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1057" t="str">
+        <x:v>Délai d’inactivité (minutes)</x:v>
+      </x:c>
+      <x:c r="E1057" t="str">
+        <x:v>Inactivity delay (minutes)</x:v>
+      </x:c>
+      <x:c r="F1057" t="str">
+        <x:v>Tiempo de inactividad (minutos)</x:v>
+      </x:c>
+      <x:c r="G1057" t="str">
+        <x:v>Inaktivitätsdauer (Minuten)</x:v>
+      </x:c>
+      <x:c r="H1057" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1057" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1057" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1058">
+      <x:c r="A1058" t="str">
+        <x:v>settings.runpod_auto_stop_hint</x:v>
+      </x:c>
+      <x:c r="B1058" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1058" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1058" t="str">
+        <x:v>Le compte à rebours commence après la dernière requête terminée. Une génération de texte ou d’image, un envoi ou un téléchargement en cours empêche l’arrêt. Un crash ou une coupure ne permet pas de garantir la commande d’arrêt : vérifie le tableau de bord Runpod.</x:v>
+      </x:c>
+      <x:c r="E1058" t="str">
+        <x:v>The countdown starts after the last completed request. Active text or image generation, upload, or download prevents automatic stop. A crash or power loss cannot guarantee the stop command; verify the Runpod dashboard.</x:v>
+      </x:c>
+      <x:c r="F1058" t="str">
+        <x:v>La cuenta atrás empieza tras la última solicitud terminada. Una generación de texto o imagen, una subida o una descarga activa evita la detención. Un fallo o corte eléctrico no garantiza la orden de parada; comprueba el panel de Runpod.</x:v>
+      </x:c>
+      <x:c r="G1058" t="str">
+        <x:v>Der Countdown beginnt nach der letzten abgeschlossenen Anfrage. Laufende Text- oder Bildgenerierung sowie Uploads oder Downloads verhindern den Stopp. Bei Absturz oder Stromausfall kann der Stoppbefehl nicht garantiert werden; prüfe das Runpod-Dashboard.</x:v>
+      </x:c>
+      <x:c r="H1058" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1058" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1058" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1059">
+      <x:c r="A1059" t="str">
+        <x:v>settings.models_reading</x:v>
+      </x:c>
+      <x:c r="B1059" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1059" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1059" t="str">
+        <x:v>Lecture des modèles depuis {provider}…</x:v>
+      </x:c>
+      <x:c r="E1059" t="str">
+        <x:v>Reading models from {provider}…</x:v>
+      </x:c>
+      <x:c r="F1059" t="str">
+        <x:v>Leyendo modelos desde {provider}…</x:v>
+      </x:c>
+      <x:c r="G1059" t="str">
+        <x:v>Modelle werden von {provider} gelesen…</x:v>
+      </x:c>
+      <x:c r="H1059" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1059" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1059" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1060">
+      <x:c r="A1060" t="str">
+        <x:v>settings.models_exposed</x:v>
+      </x:c>
+      <x:c r="B1060" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1060" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1060" t="str">
+        <x:v>{count} modèle(s) exposé(s) par {provider}.</x:v>
+      </x:c>
+      <x:c r="E1060" t="str">
+        <x:v>{count} model(s) exposed by {provider}.</x:v>
+      </x:c>
+      <x:c r="F1060" t="str">
+        <x:v>{count} modelo(s) expuesto(s) por {provider}.</x:v>
+      </x:c>
+      <x:c r="G1060" t="str">
+        <x:v>{count} Modell(e) von {provider} bereitgestellt.</x:v>
+      </x:c>
+      <x:c r="H1060" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1060" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1060" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1061">
+      <x:c r="A1061" t="str">
+        <x:v>settings.provider_unavailable</x:v>
+      </x:c>
+      <x:c r="B1061" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1061" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1061" t="str">
+        <x:v>{provider} est indisponible.</x:v>
+      </x:c>
+      <x:c r="E1061" t="str">
+        <x:v>{provider} is unavailable.</x:v>
+      </x:c>
+      <x:c r="F1061" t="str">
+        <x:v>{provider} no está disponible.</x:v>
+      </x:c>
+      <x:c r="G1061" t="str">
+        <x:v>{provider} ist nicht verfügbar.</x:v>
+      </x:c>
+      <x:c r="H1061" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1061" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1061" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1062">
+      <x:c r="A1062" t="str">
+        <x:v>settings.model_not_exposed</x:v>
+      </x:c>
+      <x:c r="B1062" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1062" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1062" t="str">
+        <x:v>{model} (non exposé actuellement)</x:v>
+      </x:c>
+      <x:c r="E1062" t="str">
+        <x:v>{model} (not currently exposed)</x:v>
+      </x:c>
+      <x:c r="F1062" t="str">
+        <x:v>{model} (no expuesto actualmente)</x:v>
+      </x:c>
+      <x:c r="G1062" t="str">
+        <x:v>{model} (derzeit nicht bereitgestellt)</x:v>
+      </x:c>
+      <x:c r="H1062" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1062" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1062" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1063">
+      <x:c r="A1063" t="str">
+        <x:v>settings.key_saved</x:v>
+      </x:c>
+      <x:c r="B1063" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1063" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1063" t="str">
+        <x:v>✓ {label} enregistrée dans {storage}</x:v>
+      </x:c>
+      <x:c r="E1063" t="str">
+        <x:v>✓ {label} saved in {storage}</x:v>
+      </x:c>
+      <x:c r="F1063" t="str">
+        <x:v>✓ {label} guardada en {storage}</x:v>
+      </x:c>
+      <x:c r="G1063" t="str">
+        <x:v>✓ {label} in {storage} gespeichert</x:v>
+      </x:c>
+      <x:c r="H1063" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1063" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1063" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1064">
+      <x:c r="A1064" t="str">
+        <x:v>settings.key_not_configured</x:v>
+      </x:c>
+      <x:c r="B1064" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1064" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1064" t="str">
+        <x:v>{label} non configurée.</x:v>
+      </x:c>
+      <x:c r="E1064" t="str">
+        <x:v>{label} not configured.</x:v>
+      </x:c>
+      <x:c r="F1064" t="str">
+        <x:v>{label} no configurada.</x:v>
+      </x:c>
+      <x:c r="G1064" t="str">
+        <x:v>{label} nicht konfiguriert.</x:v>
+      </x:c>
+      <x:c r="H1064" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1064" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1064" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1065">
+      <x:c r="A1065" t="str">
+        <x:v>settings.key_runpod_label</x:v>
+      </x:c>
+      <x:c r="B1065" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1065" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1065" t="str">
+        <x:v>Clé du compte Runpod</x:v>
+      </x:c>
+      <x:c r="E1065" t="str">
+        <x:v>Runpod account key</x:v>
+      </x:c>
+      <x:c r="F1065" t="str">
+        <x:v>Clave de la cuenta Runpod</x:v>
+      </x:c>
+      <x:c r="G1065" t="str">
+        <x:v>Runpod-Kontoschlüssel</x:v>
+      </x:c>
+      <x:c r="H1065" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1065" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1065" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1066">
+      <x:c r="A1066" t="str">
+        <x:v>settings.key_llm_label</x:v>
+      </x:c>
+      <x:c r="B1066" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1066" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1066" t="str">
+        <x:v>Clé du service LLM</x:v>
+      </x:c>
+      <x:c r="E1066" t="str">
+        <x:v>LLM service key</x:v>
+      </x:c>
+      <x:c r="F1066" t="str">
+        <x:v>Clave del servicio LLM</x:v>
+      </x:c>
+      <x:c r="G1066" t="str">
+        <x:v>LLM-Dienstschlüssel</x:v>
+      </x:c>
+      <x:c r="H1066" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1066" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1066" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1067">
+      <x:c r="A1067" t="str">
+        <x:v>settings.key_image_label</x:v>
+      </x:c>
+      <x:c r="B1067" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1067" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1067" t="str">
+        <x:v>Clé du service d’image</x:v>
+      </x:c>
+      <x:c r="E1067" t="str">
+        <x:v>Image service key</x:v>
+      </x:c>
+      <x:c r="F1067" t="str">
+        <x:v>Clave del servicio de imagen</x:v>
+      </x:c>
+      <x:c r="G1067" t="str">
+        <x:v>Bilddienstschlüssel</x:v>
+      </x:c>
+      <x:c r="H1067" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1067" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1067" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1068">
+      <x:c r="A1068" t="str">
+        <x:v>settings.secure_storage</x:v>
+      </x:c>
+      <x:c r="B1068" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1068" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1068" t="str">
+        <x:v>le stockage sécurisé</x:v>
+      </x:c>
+      <x:c r="E1068" t="str">
+        <x:v>secure storage</x:v>
+      </x:c>
+      <x:c r="F1068" t="str">
+        <x:v>almacenamiento seguro</x:v>
+      </x:c>
+      <x:c r="G1068" t="str">
+        <x:v>sicherem Speicher</x:v>
+      </x:c>
+      <x:c r="H1068" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1068" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1068" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1069">
+      <x:c r="A1069" t="str">
+        <x:v>settings.checking_provider</x:v>
+      </x:c>
+      <x:c r="B1069" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1069" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1069" t="str">
+        <x:v>Vérification de {provider}…</x:v>
+      </x:c>
+      <x:c r="E1069" t="str">
+        <x:v>Checking {provider}…</x:v>
+      </x:c>
+      <x:c r="F1069" t="str">
+        <x:v>Comprobando {provider}…</x:v>
+      </x:c>
+      <x:c r="G1069" t="str">
+        <x:v>{provider} wird geprüft…</x:v>
+      </x:c>
+      <x:c r="H1069" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1069" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1069" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1070">
+      <x:c r="A1070" t="str">
+        <x:v>settings.provider_connected</x:v>
+      </x:c>
+      <x:c r="B1070" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1070" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1070" t="str">
+        <x:v>✓ {provider} connecté</x:v>
+      </x:c>
+      <x:c r="E1070" t="str">
+        <x:v>✓ {provider} connected</x:v>
+      </x:c>
+      <x:c r="F1070" t="str">
+        <x:v>✓ {provider} conectado</x:v>
+      </x:c>
+      <x:c r="G1070" t="str">
+        <x:v>✓ {provider} verbunden</x:v>
+      </x:c>
+      <x:c r="H1070" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1070" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1070" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1071">
+      <x:c r="A1071" t="str">
+        <x:v>settings.provider_unreachable</x:v>
+      </x:c>
+      <x:c r="B1071" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1071" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1071" t="str">
+        <x:v>{provider} inaccessible</x:v>
+      </x:c>
+      <x:c r="E1071" t="str">
+        <x:v>{provider} unreachable</x:v>
+      </x:c>
+      <x:c r="F1071" t="str">
+        <x:v>{provider} inaccesible</x:v>
+      </x:c>
+      <x:c r="G1071" t="str">
+        <x:v>{provider} nicht erreichbar</x:v>
+      </x:c>
+      <x:c r="H1071" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1071" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1071" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1072">
+      <x:c r="A1072" t="str">
+        <x:v>settings.available_model_ids</x:v>
+      </x:c>
+      <x:c r="B1072" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1072" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1072" t="str">
+        <x:v>Identifiants disponibles : {models}</x:v>
+      </x:c>
+      <x:c r="E1072" t="str">
+        <x:v>Available model IDs: {models}</x:v>
+      </x:c>
+      <x:c r="F1072" t="str">
+        <x:v>IDs de modelo disponibles: {models}</x:v>
+      </x:c>
+      <x:c r="G1072" t="str">
+        <x:v>Verfügbare Modell-IDs: {models}</x:v>
+      </x:c>
+      <x:c r="H1072" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1072" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1072" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1073">
+      <x:c r="A1073" t="str">
+        <x:v>settings.pod_unknown</x:v>
+      </x:c>
+      <x:c r="B1073" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1073" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1073" t="str">
+        <x:v>état inconnu</x:v>
+      </x:c>
+      <x:c r="E1073" t="str">
+        <x:v>unknown status</x:v>
+      </x:c>
+      <x:c r="F1073" t="str">
+        <x:v>estado desconocido</x:v>
+      </x:c>
+      <x:c r="G1073" t="str">
+        <x:v>unbekannter Status</x:v>
+      </x:c>
+      <x:c r="H1073" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1073" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1073" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1074">
+      <x:c r="A1074" t="str">
+        <x:v>settings.pod_not_configured</x:v>
+      </x:c>
+      <x:c r="B1074" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1074" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1074" t="str">
+        <x:v>non configuré</x:v>
+      </x:c>
+      <x:c r="E1074" t="str">
+        <x:v>not configured</x:v>
+      </x:c>
+      <x:c r="F1074" t="str">
+        <x:v>no configurado</x:v>
+      </x:c>
+      <x:c r="G1074" t="str">
+        <x:v>nicht konfiguriert</x:v>
+      </x:c>
+      <x:c r="H1074" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1074" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1074" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1075">
+      <x:c r="A1075" t="str">
+        <x:v>settings.pod_auto_stop_in</x:v>
+      </x:c>
+      <x:c r="B1075" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1075" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1075" t="str">
+        <x:v>{status} · arrêt automatique dans {minutes} min</x:v>
+      </x:c>
+      <x:c r="E1075" t="str">
+        <x:v>{status} · auto-stop in {minutes} min</x:v>
+      </x:c>
+      <x:c r="F1075" t="str">
+        <x:v>{status} · parada automática en {minutes} min</x:v>
+      </x:c>
+      <x:c r="G1075" t="str">
+        <x:v>{status} · automatischer Stopp in {minutes} Min.</x:v>
+      </x:c>
+      <x:c r="H1075" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1075" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1075" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1076">
+      <x:c r="A1076" t="str">
+        <x:v>settings.pod_action_start</x:v>
+      </x:c>
+      <x:c r="B1076" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1076" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1076" t="str">
+        <x:v>démarrage</x:v>
+      </x:c>
+      <x:c r="E1076" t="str">
+        <x:v>starting</x:v>
+      </x:c>
+      <x:c r="F1076" t="str">
+        <x:v>iniciando</x:v>
+      </x:c>
+      <x:c r="G1076" t="str">
+        <x:v>Start läuft</x:v>
+      </x:c>
+      <x:c r="H1076" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1076" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1076" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1077">
+      <x:c r="A1077" t="str">
+        <x:v>settings.pod_action_stop</x:v>
+      </x:c>
+      <x:c r="B1077" t="str">
+        <x:v>settings</x:v>
+      </x:c>
+      <x:c r="C1077" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1077" t="str">
+        <x:v>arrêt</x:v>
+      </x:c>
+      <x:c r="E1077" t="str">
+        <x:v>stopping</x:v>
+      </x:c>
+      <x:c r="F1077" t="str">
+        <x:v>deteniendo</x:v>
+      </x:c>
+      <x:c r="G1077" t="str">
+        <x:v>Stopp läuft</x:v>
+      </x:c>
+      <x:c r="H1077" t="str">
+        <x:v>Added by v40.1.0 remote providers UI</x:v>
+      </x:c>
+      <x:c r="I1077" t="str">
+        <x:v>resources/i18n/locales/*.json</x:v>
+      </x:c>
+      <x:c r="J1077" t="str">
         <x:v>ok</x:v>
       </x:c>
     </x:row>
@@ -32281,7 +34273,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>40.0.9</x:v>
+        <x:v>40.1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
